--- a/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1945.065676624701</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1944.815962421211</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3695.966814266062</v>
+        <v>27.74502081770338</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.00584191586371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.15540347000338</v>
       </c>
     </row>
   </sheetData>
@@ -692,13 +692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2206.212709731472</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2043.986428842242</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3615.529465566531</v>
+        <v>30.5409352808537</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.77164516313428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.99323936650039</v>
       </c>
     </row>
   </sheetData>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1924.806185195583</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2840.831170518461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2166.464782650059</v>
+        <v>33.766730471054</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.90683852044639</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.78903395811609</v>
       </c>
     </row>
   </sheetData>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1853.381512523799</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3812.222238124293</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2620.199874185509</v>
+        <v>31.39288805582899</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.52106038262849</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.6317364583287</v>
       </c>
     </row>
   </sheetData>
@@ -842,13 +842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1404.637008842053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3513.311430773741</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4252.008534178298</v>
+        <v>31.97739872353332</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.0061631590617</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.26321012009231</v>
       </c>
     </row>
   </sheetData>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2552.261059743732</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4314.114543435261</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2138.709086958018</v>
+        <v>29.88712868545984</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.61145386608971</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.57635729965533</v>
       </c>
     </row>
   </sheetData>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2699.427888754243</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4606.476437442319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3571.367428421799</v>
+        <v>17.31334418865518</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.45872811235393</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.69564295165014</v>
       </c>
     </row>
   </sheetData>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2026.84408745702</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3874.978020877249</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1798.152460849832</v>
+        <v>28.44990535924939</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.0227878877521</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.82132692293983</v>
       </c>
     </row>
   </sheetData>
@@ -1042,13 +1042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2250.502576245014</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4759.181068867018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4447.049019956325</v>
+        <v>29.2979666246661</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.01681951282242</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.42182889022934</v>
       </c>
     </row>
   </sheetData>
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2995.334854786512</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1799.579583432919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2700.550529759571</v>
+        <v>32.31654718908261</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.73226718957623</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.54960095028495</v>
       </c>
     </row>
   </sheetData>
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2906.814313552039</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3443.813586073447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5018.11240870497</v>
+        <v>29.50691434819468</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.08276419607105</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.21756735015666</v>
       </c>
     </row>
   </sheetData>
@@ -1192,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2756.175485064409</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2112.733560945807</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3345.864469279937</v>
+        <v>35.95944066503571</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.73217289756355</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.16521033477764</v>
       </c>
     </row>
   </sheetData>
@@ -1242,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3509.204977371567</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1562.676932547879</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4670.433066681632</v>
+        <v>31.3422663643955</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.68430793015799</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.14948561767331</v>
       </c>
     </row>
   </sheetData>
@@ -1292,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2082.204063209478</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2608.810555450799</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2776.407215699532</v>
+        <v>26.01588792387204</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.42806277440786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.30735573390609</v>
       </c>
     </row>
   </sheetData>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2392.668428773481</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3381.477274021835</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2102.053182705896</v>
+        <v>24.64925399659345</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.8087806179975</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.14447537694776</v>
       </c>
     </row>
   </sheetData>
@@ -1392,13 +1392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2124.986559798015</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4094.467830205249</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4251.587061765395</v>
+        <v>22.64250435103703</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.44093144325945</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.70027692075946</v>
       </c>
     </row>
   </sheetData>
@@ -1442,13 +1442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4074.700770053601</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3871.168040734577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4483.010930000371</v>
+        <v>34.16436687237122</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.31071219982051</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.59896623766496</v>
       </c>
     </row>
   </sheetData>
@@ -1492,13 +1492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2072.069024483</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5905.087146667255</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2816.245630432129</v>
+        <v>30.79485613395953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.19799137020305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.61748807416949</v>
       </c>
     </row>
   </sheetData>
@@ -1542,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2151.232167791463</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3725.260628257824</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3708.953710593446</v>
+        <v>27.56113731077717</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.6348419047252</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.39503703876958</v>
       </c>
     </row>
   </sheetData>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1786.205233839848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2990.239195494272</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2835.188810274452</v>
+        <v>24.93343913555355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.60332032834264</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.82696559626786</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3315.498835559769</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2133.953944075527</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2433.891383186692</v>
+        <v>27.67958583792092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.76656430368989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.09408697711469</v>
       </c>
     </row>
   </sheetData>
@@ -1692,13 +1692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1806.418710076064</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1636.256962319319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2475.469706715353</v>
+        <v>24.92613209629851</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.25270860103502</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.00522089914634</v>
       </c>
     </row>
   </sheetData>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2709.09093543001</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6025.814925793657</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2619.364366576443</v>
+        <v>24.13995937277194</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.2367164624049</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.79294184187082</v>
       </c>
     </row>
   </sheetData>
@@ -1792,13 +1792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1879.275639202938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3151.817748419763</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3417.805220461534</v>
+        <v>26.47706601552773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.28861081487083</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.2116200015935</v>
       </c>
     </row>
   </sheetData>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1053.785597444729</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3221.968561341188</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4484.181470902372</v>
+        <v>23.60073872321084</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.27139167645984</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.24701373639218</v>
       </c>
     </row>
   </sheetData>
@@ -1892,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1849.438535944412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2486.495332099524</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3203.719297175258</v>
+        <v>26.7913896208435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.3299700939179</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.21471513898427</v>
       </c>
     </row>
   </sheetData>
@@ -1942,13 +1942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2011.95207057453</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5372.416979247536</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3293.189595559033</v>
+        <v>30.68314677769287</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.50261368260747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.24558922917432</v>
       </c>
     </row>
   </sheetData>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2734.071295385619</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2897.894903971054</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3264.67766692079</v>
+        <v>20.51219417488901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.55618956330333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.99265873549361</v>
       </c>
     </row>
   </sheetData>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2955.122239309328</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3238.89985331438</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3407.754667564439</v>
+        <v>29.85108209863836</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.27559942931564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.07366528782238</v>
       </c>
     </row>
   </sheetData>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1864.493028144056</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5179.034207945838</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3577.417503525126</v>
+        <v>33.88714808285309</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.3746731971448</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.31931822536041</v>
       </c>
     </row>
   </sheetData>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1696.940553933078</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3730.554397340937</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3494.085060451315</v>
+        <v>31.43708233264429</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.05286004466709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.26588801193076</v>
       </c>
     </row>
   </sheetData>
@@ -2192,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2128.524953907824</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1972.534921897337</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3641.21609011805</v>
+        <v>25.48623081142422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.44742128998976</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.02300714629679</v>
       </c>
     </row>
   </sheetData>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1528.33310729463</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2208.540976467069</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6486.104520693834</v>
+        <v>32.65089628343836</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.2988526102226</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.01057220018551</v>
       </c>
     </row>
   </sheetData>
@@ -2292,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1967.156365323167</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3429.948238785109</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3903.721360625028</v>
+        <v>33.38356471319422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.51512223292893</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.61565443989069</v>
       </c>
     </row>
   </sheetData>
@@ -2342,13 +2342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3071.974605207332</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2387.410589359793</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3937.466830229832</v>
+        <v>29.91266759453027</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.07682335714456</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.06460456113445</v>
       </c>
     </row>
   </sheetData>
@@ -2392,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1454.58828593391</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3078.517270578163</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3326.663323049878</v>
+        <v>30.38942990319748</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.8638766280949</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.18020754900619</v>
       </c>
     </row>
   </sheetData>
@@ -2442,13 +2442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2837.839094977287</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2378.785778992032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2990.014358666142</v>
+        <v>33.73758140049727</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.3232448322464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.11013044379186</v>
       </c>
     </row>
   </sheetData>
@@ -2492,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1956.835329158803</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3587.9274272223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1906.505087264633</v>
+        <v>30.2128587973432</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.57939289796248</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.16239228194458</v>
       </c>
     </row>
   </sheetData>
@@ -2542,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2058.342687125723</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3730.471637433853</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4152.987898613092</v>
+        <v>32.47421279510973</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.02968778100254</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.89155446459784</v>
       </c>
     </row>
   </sheetData>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3470.37331825452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1675.977571150025</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3218.711125305633</v>
+        <v>31.40226771707079</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.70307980510227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.66279798284786</v>
       </c>
     </row>
   </sheetData>
@@ -2642,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2016.450710128624</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3693.289711487196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4814.38824072305</v>
+        <v>30.28637011833866</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.74720521016359</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.81471380407578</v>
       </c>
     </row>
   </sheetData>
@@ -2692,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2037.227453952464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2582.49581305457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3587.672737459798</v>
+        <v>28.88776765915236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.49964786145236</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.24014692337992</v>
       </c>
     </row>
   </sheetData>
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1310.141299050541</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4974.151875918904</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3683.976714968302</v>
+        <v>25.39907144822501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.50612737473913</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.16796841424725</v>
       </c>
     </row>
   </sheetData>
@@ -2792,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2787.528036068563</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2525.583003907205</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3618.950421960227</v>
+        <v>35.34852615044205</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.13435708484787</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.18871218837189</v>
       </c>
     </row>
   </sheetData>
@@ -2842,13 +2842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2157.308315616963</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3466.474035005812</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3266.302087156124</v>
+        <v>27.83245405379334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.97945227192306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.51736735331372</v>
       </c>
     </row>
   </sheetData>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2942.611713969343</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2238.586905299707</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2682.139784382483</v>
+        <v>28.49208964467499</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.69487777450192</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.16829767631</v>
       </c>
     </row>
   </sheetData>
@@ -2942,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2898.255344023103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4958.261430431429</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2923.199865265217</v>
+        <v>28.76255573994925</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.12597904779533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.63882050103252</v>
       </c>
     </row>
   </sheetData>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2450.079316825321</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2613.010718074574</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3127.209792428032</v>
+        <v>24.50792929804735</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.56090814074126</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.05123574494049</v>
       </c>
     </row>
   </sheetData>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1877.893503032913</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3340.309590555537</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3886.41356389925</v>
+        <v>28.82185198641799</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.45356521778755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.14569030314443</v>
       </c>
     </row>
   </sheetData>
@@ -3092,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2820.664501610171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2736.649492194943</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3578.764835204235</v>
+        <v>28.35928984903407</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.02315334752287</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.25320794296617</v>
       </c>
     </row>
   </sheetData>
@@ -3142,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2815.724143032312</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3415.396342586146</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3406.974606451903</v>
+        <v>27.36249066635673</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.17845929038437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.27195059099135</v>
       </c>
     </row>
   </sheetData>
@@ -3192,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2337.441659592988</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2385.394333998585</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2331.583709752465</v>
+        <v>26.11315560430765</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.97538476397806</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.09639958000476</v>
       </c>
     </row>
   </sheetData>
@@ -3242,13 +3242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1338.52374965279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3614.706644664839</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5512.209300126161</v>
+        <v>23.65332856638072</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.39452266423224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.10000780110029</v>
       </c>
     </row>
   </sheetData>
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2581.345203136867</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2714.189886700981</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5371.648128949487</v>
+        <v>25.60450654482359</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.44614569500601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.33226320323581</v>
       </c>
     </row>
   </sheetData>
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1904.983660906142</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2798.61940505759</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2784.155600726859</v>
+        <v>32.01300601691825</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.03125433942662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.09045388810773</v>
       </c>
     </row>
   </sheetData>
@@ -3392,13 +3392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1741.552257748004</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2292.618846967813</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3309.776955606411</v>
+        <v>31.10950253953569</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.45066786094034</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.27100603342128</v>
       </c>
     </row>
   </sheetData>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3386.783652981903</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4472.353161247292</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2152.618069777992</v>
+        <v>27.56034650020127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.10616802428082</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.25348224944623</v>
       </c>
     </row>
   </sheetData>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2161.787672808072</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3576.810561421526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5321.001830890776</v>
+        <v>32.11682829806787</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.67085907026237</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.18019819141083</v>
       </c>
     </row>
   </sheetData>
@@ -3542,13 +3542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1867.535771566925</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3601.628111938217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6029.262322160344</v>
+        <v>29.16867610584845</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.38817985507696</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.90536206485579</v>
       </c>
     </row>
   </sheetData>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2121.625627998258</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4373.421042092952</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2503.101362762077</v>
+        <v>26.78181720298786</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.51931039420756</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.65258877952407</v>
       </c>
     </row>
   </sheetData>
@@ -3642,13 +3642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2860.528195106668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4358.317734828418</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2782.977208358495</v>
+        <v>27.81486158842916</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.96337093073547</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.90002831589453</v>
       </c>
     </row>
   </sheetData>
@@ -3692,13 +3692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1331.200531305798</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1894.176286594908</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2894.4823796095</v>
+        <v>22.72840043137299</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.52809279424521</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.21038940359906</v>
       </c>
     </row>
   </sheetData>
@@ -3742,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2354.24398546872</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2656.561992556877</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3054.434085757651</v>
+        <v>32.50751996098155</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.56520798349186</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.86326155415856</v>
       </c>
     </row>
   </sheetData>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1979.390086156529</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2379.821201893661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4440.021253413687</v>
+        <v>32.23827679979077</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.05833964633681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.4099823976256</v>
       </c>
     </row>
   </sheetData>
@@ -3842,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1917.064720907747</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3663.064993806546</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3569.902638174715</v>
+        <v>29.44709796890797</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.46436981860043</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.78542138480404</v>
       </c>
     </row>
   </sheetData>
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2731.991894046101</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4036.904500493038</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1854.728229696323</v>
+        <v>26.6431699663916</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.51028743174671</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.96385201170354</v>
       </c>
     </row>
   </sheetData>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1613.598352934497</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3324.810233176679</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5869.11567917029</v>
+        <v>27.70960377274469</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.07977657038514</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.66796275147769</v>
       </c>
     </row>
   </sheetData>
@@ -3992,13 +3992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1894.242028891207</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3093.882259940631</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4429.105116982136</v>
+        <v>37.24307721477866</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.27650116974506</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.48792945898501</v>
       </c>
     </row>
   </sheetData>
@@ -4042,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1689.839052533057</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2224.393414322355</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3375.31785524545</v>
+        <v>36.16314442815045</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.09106977120194</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.51164489422285</v>
       </c>
     </row>
   </sheetData>
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1968.182565472218</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2991.009314644533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3487.64760157241</v>
+        <v>32.29672913987452</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.10248317403946</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.06206430926031</v>
       </c>
     </row>
   </sheetData>
@@ -4142,13 +4142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1789.504257902462</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3900.704308465088</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2264.452146515353</v>
+        <v>24.76785585863886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.63220132299359</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.65505720630234</v>
       </c>
     </row>
   </sheetData>
@@ -4192,13 +4192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2505.523777611556</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4276.623388023762</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2732.09282366603</v>
+        <v>32.92861638304133</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.33902582272414</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.03338844526447</v>
       </c>
     </row>
   </sheetData>
@@ -4242,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2916.966461266108</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2996.736877510654</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2630.635898656567</v>
+        <v>26.21721734674357</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.2649047324988</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.20759099737668</v>
       </c>
     </row>
   </sheetData>
@@ -4292,13 +4292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1353.824873446465</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2612.835248798138</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6082.884577898296</v>
+        <v>30.35514890049568</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.12565233452127</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.06006323436851</v>
       </c>
     </row>
   </sheetData>
@@ -4342,13 +4342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1602.417409227455</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2699.46152075205</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3736.33461541911</v>
+        <v>33.60686143160655</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.51907063042826</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.34738853360872</v>
       </c>
     </row>
   </sheetData>
@@ -4392,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3706.049322424851</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1970.439415688266</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2556.694316676764</v>
+        <v>21.32342932954371</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.16913342824716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.53996875150363</v>
       </c>
     </row>
   </sheetData>
@@ -4442,13 +4442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1889.317857327565</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3575.020516449219</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3487.885887943411</v>
+        <v>25.5591942445246</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.01324829392547</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.46976369998896</v>
       </c>
     </row>
   </sheetData>
@@ -4492,13 +4492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4145.22736255555</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2608.830593043453</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2512.79694418248</v>
+        <v>27.99540148718498</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.33892089153401</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.02228707559464</v>
       </c>
     </row>
   </sheetData>
@@ -4542,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2377.629443750815</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3088.844736422413</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4163.371153163466</v>
+        <v>21.16421665220624</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.54319563423561</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.88038706960233</v>
       </c>
     </row>
   </sheetData>
@@ -4592,13 +4592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2053.963390331677</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3622.040833272457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3416.392313961906</v>
+        <v>24.56667881478189</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.37864292838509</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.91602179128753</v>
       </c>
     </row>
   </sheetData>
@@ -4642,13 +4642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3401.237956897418</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2668.618404861823</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3523.66817916781</v>
+        <v>27.90394395046667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.3485669632909</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.97677489574351</v>
       </c>
     </row>
   </sheetData>
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2996.727650644582</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3427.191017852714</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2954.714215462623</v>
+        <v>30.66754427951156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.75663138182476</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.42645840768514</v>
       </c>
     </row>
   </sheetData>
@@ -4742,13 +4742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1803.946190296322</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3043.333607410899</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3891.850012250605</v>
+        <v>25.35357196555821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.46994256603974</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.59882797484341</v>
       </c>
     </row>
   </sheetData>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1342.153243044859</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3308.661293729348</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3905.789314687424</v>
+        <v>28.95780701726897</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.94523872153529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.14922320741784</v>
       </c>
     </row>
   </sheetData>
@@ -4842,13 +4842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2207.490311744755</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2705.874144331532</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1895.160793004293</v>
+        <v>27.08930568980784</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.72775465338477</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.93695079176249</v>
       </c>
     </row>
   </sheetData>
@@ -4892,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2470.084047513452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2954.740223678726</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3162.689806983056</v>
+        <v>18.51411787789205</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.35614157110785</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.00526830028424</v>
       </c>
     </row>
   </sheetData>
@@ -4942,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2137.349973679806</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2536.207176231641</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4105.120983654346</v>
+        <v>23.72334917117123</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.1603842548346</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.14882280839786</v>
       </c>
     </row>
   </sheetData>
@@ -4992,13 +4992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2067.273239862845</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3601.710179674893</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2719.71980822911</v>
+        <v>24.53046519816744</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.81228479994825</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.05342748917449</v>
       </c>
     </row>
   </sheetData>
@@ -5042,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2396.420468983147</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4064.92743873995</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3948.076613168086</v>
+        <v>25.72530962866869</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.92471675415169</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.95746773394413</v>
       </c>
     </row>
   </sheetData>
@@ -5092,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1860.599715884418</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3527.233366919881</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2132.297410194163</v>
+        <v>25.44879892648938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.89288689695061</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.36112985337611</v>
       </c>
     </row>
   </sheetData>
@@ -5142,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1849.939279513491</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3671.689193942446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2826.197345702114</v>
+        <v>30.08936745703356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.09724960237404</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.33440173777834</v>
       </c>
     </row>
   </sheetData>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2697.814427533718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3859.574606312989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2542.547436970297</v>
+        <v>24.59991587282883</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.40115808607575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.83606840785914</v>
       </c>
     </row>
   </sheetData>
@@ -5242,13 +5242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3961.552510068436</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2165.139164939651</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2803.298783121406</v>
+        <v>27.365224356249</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.76350061281807</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.16523163495244</v>
       </c>
     </row>
   </sheetData>
@@ -5292,13 +5292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1736.856985321304</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3333.683489910446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3235.239973878759</v>
+        <v>30.35032851819323</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.90277169251232</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.46477452280219</v>
       </c>
     </row>
   </sheetData>
@@ -5342,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1363.241256061655</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3445.028009052209</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3380.430441243167</v>
+        <v>24.23027865296353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.7421088926628</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.9603607497911</v>
       </c>
     </row>
   </sheetData>
@@ -5392,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1845.342963828202</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5219.299696309043</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4514.585409937321</v>
+        <v>31.96145640040172</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.76943830231313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.91733380173432</v>
       </c>
     </row>
   </sheetData>
@@ -5442,13 +5442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3222.78228007525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3961.222367278961</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2626.153630808603</v>
+        <v>26.91515971286996</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.80421112538723</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.93070357990063</v>
       </c>
     </row>
   </sheetData>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2036.406130756191</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2237.755811786532</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3763.518952445657</v>
+        <v>21.98392499894932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.32626151083153</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.58795806587868</v>
       </c>
     </row>
   </sheetData>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2001.534795571856</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2490.895733586013</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3853.730664782569</v>
+        <v>25.00592971409452</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.38405803620814</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.61096594601325</v>
       </c>
     </row>
   </sheetData>
@@ -5592,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2336.991858407686</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3299.118786373584</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1943.653506114299</v>
+        <v>28.49627078124718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.05616125683886</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.12179594359247</v>
       </c>
     </row>
   </sheetData>
@@ -5642,13 +5642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2763.065438851205</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2700.890263918514</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2506.800265878008</v>
+        <v>25.96200971413042</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.42204574082663</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.36798292818193</v>
       </c>
     </row>
   </sheetData>
@@ -5692,13 +5692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1186.842740160076</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3918.50801131281</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2731.28246965455</v>
+        <v>30.16508413371342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.37565127747876</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.73173341065887</v>
       </c>
     </row>
   </sheetData>
@@ -5742,13 +5742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2459.551538885299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4609.627010059842</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3022.871879528062</v>
+        <v>34.74156170017256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.40810529695036</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.13383907545784</v>
       </c>
     </row>
   </sheetData>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2097.816830654676</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2671.804997020822</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1943.73193351499</v>
+        <v>28.7319921486092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.75497357713646</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.80670254293761</v>
       </c>
     </row>
   </sheetData>
@@ -5842,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1278.523434766152</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3983.036291461526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3363.28226894709</v>
+        <v>30.26387083587054</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.42957198323728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.78581530708589</v>
       </c>
     </row>
   </sheetData>
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1813.031213031333</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3230.996876446991</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3060.705330158354</v>
+        <v>28.66950059609909</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.24665346441451</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.61338458094249</v>
       </c>
     </row>
   </sheetData>
@@ -5942,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1909.522010829521</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3847.020017589676</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3264.104747471657</v>
+        <v>23.18894283653658</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.59829517877377</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.83901740948378</v>
       </c>
     </row>
   </sheetData>
@@ -5992,13 +5992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2339.579682621057</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1977.782712048569</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3565.969594674747</v>
+        <v>29.89687520461042</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.92207285015577</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.40164678664153</v>
       </c>
     </row>
   </sheetData>
@@ -6042,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2054.732112482381</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4259.711390849554</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2454.132311041605</v>
+        <v>31.3033819872751</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.12200583434516</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.31541512936245</v>
       </c>
     </row>
   </sheetData>
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2760.877190614958</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2768.621846045721</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2997.203874995847</v>
+        <v>32.51012064687713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.54864203465145</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.55177695836077</v>
       </c>
     </row>
   </sheetData>
@@ -6142,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2001.197847636646</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3661.301522162189</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2705.450824528701</v>
+        <v>27.73542259605647</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.02873157160182</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.61250101910888</v>
       </c>
     </row>
   </sheetData>
@@ -6192,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2084.640239201993</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2661.511988040712</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3439.800028878009</v>
+        <v>26.30342772203808</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.74727492486978</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.82021569350095</v>
       </c>
     </row>
   </sheetData>
@@ -6242,13 +6242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3272.563071291986</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1658.863955808029</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2431.231321141191</v>
+        <v>25.10644669197459</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.55376150661147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.86617287622672</v>
       </c>
     </row>
   </sheetData>
@@ -6292,13 +6292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1624.065804358137</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3592.394489352559</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4284.725812374999</v>
+        <v>31.18284904144188</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.99423351795378</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.16679070606248</v>
       </c>
     </row>
   </sheetData>
@@ -6342,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2541.406719563463</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1666.749316607457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2352.459773916591</v>
+        <v>24.73046144614133</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.63382891395111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.33820969303554</v>
       </c>
     </row>
   </sheetData>
@@ -6392,13 +6392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3547.431185261345</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3469.044998921899</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1951.429648057256</v>
+        <v>29.3627033632728</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.004895322379</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.72407711382724</v>
       </c>
     </row>
   </sheetData>
@@ -6442,13 +6442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3912.936331758499</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2985.999308433105</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2002.565899195978</v>
+        <v>27.79507881987436</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.19671378589848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.38220775350576</v>
       </c>
     </row>
   </sheetData>
@@ -6492,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1942.341941795232</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3988.090079774724</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2764.01649907205</v>
+        <v>27.76841337618588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.53762415848485</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.80464872185</v>
       </c>
     </row>
   </sheetData>
@@ -6542,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2085.001328261947</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4085.975289578163</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3834.075521598738</v>
+        <v>30.36409315943309</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.22260658815705</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.504430844352</v>
       </c>
     </row>
   </sheetData>
@@ -6592,13 +6592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2364.862441750241</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2676.823568860951</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2014.0253134845</v>
+        <v>26.73709440112171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.46585622441958</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.45405431776026</v>
       </c>
     </row>
   </sheetData>
@@ -6642,13 +6642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2880.224620271863</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2548.9622142073</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2931.832590870498</v>
+        <v>30.36161543482292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.55538588699985</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.95135202461562</v>
       </c>
     </row>
   </sheetData>
@@ -6692,13 +6692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1919.566691739786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4126.438046391665</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3931.39446124393</v>
+        <v>28.68594914332985</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.66583229265814</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.23523472768553</v>
       </c>
     </row>
   </sheetData>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1907.045858055861</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3407.915952597415</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2188.68205319922</v>
+        <v>23.5561549572117</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.89178443298761</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.24369904216454</v>
       </c>
     </row>
   </sheetData>
@@ -6792,13 +6792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1804.525626498379</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2772.253987572827</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2433.086719064115</v>
+        <v>26.09336523027877</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.44347564769833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.43817997951325</v>
       </c>
     </row>
   </sheetData>
@@ -6842,13 +6842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4299.869500148141</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2060.724171336855</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4061.774333300006</v>
+        <v>25.51865683167107</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.21012425816123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.86712765528775</v>
       </c>
     </row>
   </sheetData>
@@ -6892,13 +6892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2362.623625271472</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2658.568339070973</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2931.589087111965</v>
+        <v>28.19786730914388</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.35720854554034</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.24890064294239</v>
       </c>
     </row>
   </sheetData>
@@ -6942,13 +6942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2783.514290995191</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3319.56441314256</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3939.78911402064</v>
+        <v>25.83109521973631</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.7001158800176</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.76235843536793</v>
       </c>
     </row>
   </sheetData>
@@ -6992,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2858.844744943083</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2146.489947347693</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2268.597520715864</v>
+        <v>30.18462406011791</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.0314249423125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.28223327493148</v>
       </c>
     </row>
   </sheetData>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2226.469216332387</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2368.053677357287</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4531.388561307529</v>
+        <v>26.59033415949766</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.71870056200471</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.42537312891573</v>
       </c>
     </row>
   </sheetData>
@@ -7092,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1769.38405722173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1981.352227611241</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3405.866327942326</v>
+        <v>24.08819942028322</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.21818581850279</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.48246096844848</v>
       </c>
     </row>
   </sheetData>
@@ -7142,13 +7142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3138.57875179014</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2192.03825015924</v>
-      </c>
-      <c r="D2" t="n">
-        <v>8161.656118212321</v>
+        <v>32.46467884556073</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.49285399184575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.91356735605867</v>
       </c>
     </row>
   </sheetData>
@@ -7192,13 +7192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2689.917708494197</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2890.839798009988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4413.71655228896</v>
+        <v>26.72820946207831</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.39373315630642</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.96988614234165</v>
       </c>
     </row>
   </sheetData>
@@ -7242,13 +7242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2388.542800136317</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2397.814414175668</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2900.298771881792</v>
+        <v>19.02873957021466</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.02555919909036</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.26382315236719</v>
       </c>
     </row>
   </sheetData>
@@ -7292,13 +7292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1847.602897341006</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2322.752865983694</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3352.098122765564</v>
+        <v>22.09233683455439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.31150677800116</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.75123076796193</v>
       </c>
     </row>
   </sheetData>
@@ -7342,13 +7342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1670.490242522292</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2858.231277816115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4182.779710757409</v>
+        <v>30.5158152082277</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.66360494812411</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.66324170784545</v>
       </c>
     </row>
   </sheetData>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1450.032193248519</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2725.076787911968</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3221.019548983156</v>
+        <v>29.0584939024926</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.35444921213853</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.11694880539275</v>
       </c>
     </row>
   </sheetData>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2115.400349098227</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3316.759516061087</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6253.208990133468</v>
+        <v>32.63967678766439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.82531353979533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.82291581988652</v>
       </c>
     </row>
   </sheetData>
@@ -7492,13 +7492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2020.621442647111</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2901.00420597222</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4575.311661374793</v>
+        <v>31.93420023043948</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.42588183446052</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.74906889408186</v>
       </c>
     </row>
   </sheetData>
@@ -7542,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1759.868188926018</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2795.713506334735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4306.307493312372</v>
+        <v>27.20261186501354</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.14544515404483</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.99909049638405</v>
       </c>
     </row>
   </sheetData>
@@ -7592,13 +7592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2462.33201550382</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4000.367158029666</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4496.838436114113</v>
+        <v>27.31408521150264</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.74857485092133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.46365827390901</v>
       </c>
     </row>
   </sheetData>
@@ -7642,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1731.811927524796</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2970.142428816552</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4428.821044390753</v>
+        <v>34.48298721658237</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.48723125014835</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.63482475115923</v>
       </c>
     </row>
   </sheetData>
@@ -7692,13 +7692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1626.820232419969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3405.163957331894</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2364.458580894999</v>
+        <v>24.30936555124739</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.57583508816865</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.57179573450898</v>
       </c>
     </row>
   </sheetData>
@@ -7742,13 +7742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1999.367922936796</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2493.785284137907</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5060.778775776273</v>
+        <v>23.44444623499762</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14.72508936698066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.56507799369945</v>
       </c>
     </row>
   </sheetData>
@@ -7792,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2202.129219785214</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2296.646691787083</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2295.338463300347</v>
+        <v>20.80376976506528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.28530311718316</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.89293458115825</v>
       </c>
     </row>
   </sheetData>
@@ -7842,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1296.150504472074</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3623.605840197715</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2640.753401288843</v>
+        <v>30.48301289385104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.74498640744289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.8763521633646</v>
       </c>
     </row>
   </sheetData>
@@ -7892,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3629.569194175764</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2816.51446036884</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1814.702869949387</v>
+        <v>26.41283845361352</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.19408264457036</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.82843435702108</v>
       </c>
     </row>
   </sheetData>
@@ -7942,13 +7942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1982.858410539984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3046.866290864448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2814.377733026796</v>
+        <v>28.63096648943837</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.00951367632715</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.80709433394701</v>
       </c>
     </row>
   </sheetData>
@@ -7992,13 +7992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1542.64127472016</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2937.068324386128</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4430.685313590846</v>
+        <v>27.72789121480131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.43123302338133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.13102207162143</v>
       </c>
     </row>
   </sheetData>
@@ -8042,13 +8042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1413.782868801532</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3393.339601534906</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3230.425474175277</v>
+        <v>28.74105527828652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.44625850581516</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.11991682367882</v>
       </c>
     </row>
   </sheetData>
@@ -8092,13 +8092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4343.874142962103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2015.913753402029</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4279.348688893278</v>
+        <v>31.21417997639984</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.18885931603759</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.13508689317036</v>
       </c>
     </row>
   </sheetData>
@@ -8142,13 +8142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2881.553414390906</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4294.066644411763</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2698.402653170506</v>
+        <v>28.85112949119004</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.18947409781581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.22631181383436</v>
       </c>
     </row>
   </sheetData>
@@ -8192,13 +8192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2031.868664537077</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3089.969862496334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4059.908816892885</v>
+        <v>31.38104537083225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.98067585593383</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.84749629893379</v>
       </c>
     </row>
   </sheetData>
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3728.523252866448</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1782.845300806554</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2434.182761549345</v>
+        <v>27.45377456929072</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.73563844310345</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.54969679118632</v>
       </c>
     </row>
   </sheetData>
@@ -8292,13 +8292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1931.863346025367</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3454.507681808165</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3595.444508712409</v>
+        <v>31.23177184723438</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.10611132045815</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.47871035805099</v>
       </c>
     </row>
   </sheetData>
@@ -8342,13 +8342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2500.238925507766</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3619.652709415264</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3890.809512390045</v>
+        <v>21.38179911030743</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.66495564060308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.99594790066578</v>
       </c>
     </row>
   </sheetData>
@@ -8392,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1760.678858466605</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3160.545141793677</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3382.60957184616</v>
+        <v>25.53217106917584</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.48556389160781</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.65541377492025</v>
       </c>
     </row>
   </sheetData>
@@ -8442,13 +8442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1643.153599038804</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3035.447854564347</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3467.567666702294</v>
+        <v>32.31648799767439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.42366469142474</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.97558312765094</v>
       </c>
     </row>
   </sheetData>
@@ -8492,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2676.083229661674</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2735.644976532692</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3501.968263686505</v>
+        <v>34.54800191020548</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.50821452371563</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.44589819128782</v>
       </c>
     </row>
   </sheetData>
@@ -8542,13 +8542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2124.176023720039</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2729.912826362179</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2925.212053816778</v>
+        <v>20.09998403884269</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.6176907987473</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.24183434186633</v>
       </c>
     </row>
   </sheetData>
@@ -8592,13 +8592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2350.795664843707</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2905.269963811962</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4627.31684740298</v>
+        <v>28.55081026534635</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.67428189442034</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.16578442708409</v>
       </c>
     </row>
   </sheetData>
@@ -8642,13 +8642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3825.392883851625</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2179.670313994165</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4040.846924637162</v>
+        <v>27.2483986105011</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.22553534250263</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.0840027573865</v>
       </c>
     </row>
   </sheetData>
@@ -8692,13 +8692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1984.781667572183</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2841.685083231392</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3019.133149292615</v>
+        <v>32.59778752576444</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.37436081096494</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.94585207489834</v>
       </c>
     </row>
   </sheetData>
@@ -8742,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2697.769444697641</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2877.424489093158</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3277.928670070462</v>
+        <v>24.41479618479542</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.62895040811953</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.80999478498221</v>
       </c>
     </row>
   </sheetData>
@@ -8792,13 +8792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2160.730115377341</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2009.500582620733</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3238.602110937014</v>
+        <v>27.27326067434666</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.19114899542105</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.99047438609009</v>
       </c>
     </row>
   </sheetData>
@@ -8842,13 +8842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1565.909188623234</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2567.179233763207</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2655.462280841642</v>
+        <v>27.28181491748935</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.15515937002354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.84047147184727</v>
       </c>
     </row>
   </sheetData>
@@ -8892,13 +8892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1810.318444940216</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2906.539470009148</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2965.163144514647</v>
+        <v>28.34995688551026</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.14012469620555</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.46911447740827</v>
       </c>
     </row>
   </sheetData>
@@ -8942,13 +8942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2692.28868017164</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1856.015906483535</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3349.688058545385</v>
+        <v>25.5210218688459</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.86473352654489</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.58789417388856</v>
       </c>
     </row>
   </sheetData>
@@ -8992,13 +8992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2419.424245927758</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2358.925595941921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5126.651414450424</v>
+        <v>22.68295249732611</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.63393603831371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.06107287516288</v>
       </c>
     </row>
   </sheetData>
@@ -9042,13 +9042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2257.89398368775</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3701.686268044798</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3418.524006472506</v>
+        <v>30.84782544686434</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.02548004348037</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.10951011919077</v>
       </c>
     </row>
   </sheetData>
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2031.744128068148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2672.586942229295</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5265.888096396968</v>
+        <v>23.52972175517225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.0990395132652</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.3880081689548</v>
       </c>
     </row>
   </sheetData>
@@ -9142,13 +9142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2676.832956371292</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3386.977291694738</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3467.775491475456</v>
+        <v>24.67933147653255</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.43614287874326</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.39433710558048</v>
       </c>
     </row>
   </sheetData>
@@ -9192,13 +9192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2079.162342010224</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4269.007334586321</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3458.643045531539</v>
+        <v>26.69754471552891</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.64552167426959</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.78935038252293</v>
       </c>
     </row>
   </sheetData>
@@ -9242,13 +9242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2645.869535161998</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2593.898654138115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4455.875063826591</v>
+        <v>29.26489675321843</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.57985330777584</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.03176076109498</v>
       </c>
     </row>
   </sheetData>
@@ -9292,13 +9292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1247.62968612702</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2826.913026367577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1665.160541327018</v>
+        <v>26.19626924792643</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.28479094499445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.36574290656381</v>
       </c>
     </row>
   </sheetData>
@@ -9342,13 +9342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2745.470665495953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2477.946965566922</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2732.536731268789</v>
+        <v>28.33736347570808</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.54918890534846</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.18772591181732</v>
       </c>
     </row>
   </sheetData>
@@ -9392,13 +9392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2899.934640386341</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3192.146541700275</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3952.096471793525</v>
+        <v>32.9389787971248</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.73089945971169</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.20937779766537</v>
       </c>
     </row>
   </sheetData>
@@ -9442,13 +9442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2634.013054845212</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4468.143718016481</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3202.17627884496</v>
+        <v>27.7418260192681</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.32429950891461</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.01733733796842</v>
       </c>
     </row>
   </sheetData>
@@ -9492,13 +9492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3272.494354556758</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2114.839509212575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3185.112004315519</v>
+        <v>31.8860294616693</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.19747246501421</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.34763683850856</v>
       </c>
     </row>
   </sheetData>
@@ -9542,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1371.42861378436</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3891.585993544274</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4854.032303557846</v>
+        <v>33.50706509316328</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.07496309434811</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.9276127037743</v>
       </c>
     </row>
   </sheetData>
@@ -9592,13 +9592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2073.908410820748</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3471.025921262876</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3569.918654849884</v>
+        <v>33.34099072701799</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.97340887382689</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.02904506321394</v>
       </c>
     </row>
   </sheetData>
@@ -9642,13 +9642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1953.236734297834</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4219.885921147147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3596.687494236249</v>
+        <v>35.09400056627361</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.70812154956989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.61081746460752</v>
       </c>
     </row>
   </sheetData>
@@ -9692,13 +9692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1394.624892208807</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2964.071499536555</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4739.236184330476</v>
+        <v>21.11342624035067</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.26382834209543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70826548087035</v>
       </c>
     </row>
   </sheetData>
@@ -9742,13 +9742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2198.938876475172</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2752.526321106802</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3410.632998910156</v>
+        <v>28.06563614235044</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.90653217318517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.59606749980162</v>
       </c>
     </row>
   </sheetData>
@@ -9792,13 +9792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1408.501797268347</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2676.188986815126</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4472.874562234583</v>
+        <v>28.42152263214249</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.55693696388679</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.01330275620741</v>
       </c>
     </row>
   </sheetData>
@@ -9842,13 +9842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2105.009321627884</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2729.195577134293</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2140.599373228623</v>
+        <v>23.42435880207744</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.72165141640378</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.83767745142251</v>
       </c>
     </row>
   </sheetData>
@@ -9892,13 +9892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2588.047442386343</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2871.852528432783</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2794.189491631404</v>
+        <v>22.84398245318509</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.29407563412094</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.57668991263499</v>
       </c>
     </row>
   </sheetData>
@@ -9942,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1583.307480342455</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3437.345193291492</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4032.106920633031</v>
+        <v>35.66631015348404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.6384864383167</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.57934080228413</v>
       </c>
     </row>
   </sheetData>
@@ -9992,13 +9992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2605.299614752498</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4727.637457237077</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2997.249734991426</v>
+        <v>27.1239665255933</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.0523497940352</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.52347173764035</v>
       </c>
     </row>
   </sheetData>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3389.607779253058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2964.791182703729</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2804.49763210604</v>
+        <v>31.19045131334382</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.62303454831343</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.3128298121612</v>
       </c>
     </row>
   </sheetData>
@@ -10092,13 +10092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3108.928811942944</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1674.921801577834</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2993.142287029274</v>
+        <v>33.22876797487366</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.51731919955206</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.72295077630572</v>
       </c>
     </row>
   </sheetData>
@@ -10142,13 +10142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2116.609289262942</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1432.643001462498</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3478.991559054659</v>
+        <v>28.86620065900053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.90255424595032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.31809846423743</v>
       </c>
     </row>
   </sheetData>
@@ -10192,13 +10192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2870.908295565275</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2430.125895962883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2931.183703974825</v>
+        <v>25.88923641155149</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.21582042403217</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.837142057713</v>
       </c>
     </row>
   </sheetData>
@@ -10242,13 +10242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2106.997366977693</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3509.158762803238</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5380.767125046616</v>
+        <v>29.32090985244281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.39087562166305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.94426079636484</v>
       </c>
     </row>
   </sheetData>
@@ -10292,13 +10292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4833.975466455233</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4478.588787068865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1356.010413359111</v>
+        <v>36.26761709478797</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.20935177031887</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.72025875118634</v>
       </c>
     </row>
   </sheetData>
@@ -10342,13 +10342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1507.751249854442</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2596.955844082741</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4008.736829662358</v>
+        <v>26.08560210945038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.54826840546856</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.00204866005659</v>
       </c>
     </row>
   </sheetData>
@@ -10392,13 +10392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2177.877326775745</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4522.358056630963</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3469.000964025097</v>
+        <v>23.35578882568737</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.21262916305475</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.66138218525813</v>
       </c>
     </row>
   </sheetData>
@@ -10442,13 +10442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1930.224542770702</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2660.538959991841</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3466.991547862942</v>
+        <v>30.55789517621375</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.54559375512889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.54184933434984</v>
       </c>
     </row>
   </sheetData>
@@ -10492,13 +10492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4501.908218810256</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2746.763004378755</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2485.164027245322</v>
+        <v>29.36494038365652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.50287728926058</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.54803388066104</v>
       </c>
     </row>
   </sheetData>
@@ -10542,13 +10542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2219.498747275326</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2738.169982345653</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2623.768218588478</v>
+        <v>22.49429460422881</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.13221870645768</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.02552280324668</v>
       </c>
     </row>
   </sheetData>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1552.565146489487</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5722.292155342131</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3549.236218060934</v>
+        <v>28.24401865451406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.91952642465924</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.44538793508013</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.74502081770338</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.00584191586371</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.15540347000338</v>
+        <v>24.41193106929261</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.91719270494497</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.38695220645081</v>
       </c>
     </row>
   </sheetData>
@@ -692,13 +692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.5409352808537</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.77164516313428</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.99323936650039</v>
+        <v>26.39072429262812</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.80591307656732</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.46639778637776</v>
       </c>
     </row>
   </sheetData>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.766730471054</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.90683852044639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.78903395811609</v>
+        <v>19.70876144890668</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.97895144161064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.72146366470049</v>
       </c>
     </row>
   </sheetData>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.39288805582899</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.52106038262849</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.6317364583287</v>
+        <v>21.02275075691368</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.05873015190059</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.41589139084699</v>
       </c>
     </row>
   </sheetData>
@@ -842,13 +842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.97739872353332</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.0061631590617</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.26321012009231</v>
+        <v>22.94684013011025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.34615271942581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.18051770559967</v>
       </c>
     </row>
   </sheetData>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.88712868545984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.61145386608971</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.57635729965533</v>
+        <v>25.94277236700007</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.99032621931648</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.77628524231944</v>
       </c>
     </row>
   </sheetData>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.31334418865518</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.45872811235393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.69564295165014</v>
+        <v>19.00414374952524</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.74809059079432</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.27623621817886</v>
       </c>
     </row>
   </sheetData>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.44990535924939</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.0227878877521</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.82132692293983</v>
+        <v>25.85263283285062</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.71522447067131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.02287896797837</v>
       </c>
     </row>
   </sheetData>
@@ -1042,13 +1042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.2979666246661</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.01681951282242</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.42182889022934</v>
+        <v>27.32186374844024</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.52009816276944</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.53639908356001</v>
       </c>
     </row>
   </sheetData>
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.31654718908261</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.73226718957623</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.54960095028495</v>
+        <v>20.89679877881625</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.6111879265847</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.86948854289238</v>
       </c>
     </row>
   </sheetData>
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.50691434819468</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.08276419607105</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.21756735015666</v>
+        <v>22.09172828864536</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.23560367117592</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.77713900525124</v>
       </c>
     </row>
   </sheetData>
@@ -1192,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.95944066503571</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.73217289756355</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.16521033477764</v>
+        <v>27.63872172453603</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.92436533772203</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.35519913774049</v>
       </c>
     </row>
   </sheetData>
@@ -1242,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.3422663643955</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.68430793015799</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.14948561767331</v>
+        <v>20.5667437839385</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.8241733514425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.31932335656823</v>
       </c>
     </row>
   </sheetData>
@@ -1292,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.01588792387204</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.42806277440786</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.30735573390609</v>
+        <v>20.13707272973053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.36294012461794</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.92926155460204</v>
       </c>
     </row>
   </sheetData>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.64925399659345</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.8087806179975</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.14447537694776</v>
+        <v>17.86608600286051</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.95937457868608</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.50880334370353</v>
       </c>
     </row>
   </sheetData>
@@ -1392,13 +1392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.64250435103703</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.44093144325945</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.70027692075946</v>
+        <v>20.39087685624306</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.71023904236861</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.70274452069858</v>
       </c>
     </row>
   </sheetData>
@@ -1442,13 +1442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.16436687237122</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.31071219982051</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.59896623766496</v>
+        <v>25.12540986683749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.61864735655447</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.41602481016652</v>
       </c>
     </row>
   </sheetData>
@@ -1492,13 +1492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.79485613395953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.19799137020305</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.61748807416949</v>
+        <v>18.14081511655589</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.06327408355864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.33349672177718</v>
       </c>
     </row>
   </sheetData>
@@ -1542,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.56113731077717</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.6348419047252</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.39503703876958</v>
+        <v>23.3145656909482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.58387320879106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.80854328051056</v>
       </c>
     </row>
   </sheetData>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.93343913555355</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.60332032834264</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.82696559626786</v>
+        <v>19.15469932302922</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.83373157721208</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.50261960207982</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.67958583792092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.76656430368989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.09408697711469</v>
+        <v>16.62973060989766</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.06890922811543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.16485171024601</v>
       </c>
     </row>
   </sheetData>
@@ -1692,13 +1692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.92613209629851</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.25270860103502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.00522089914634</v>
+        <v>16.23954511386913</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.5742987017859</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.80343934708014</v>
       </c>
     </row>
   </sheetData>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.13995937277194</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.2367164624049</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.79294184187082</v>
+        <v>23.67656554860938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.99483071983768</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.62273893318902</v>
       </c>
     </row>
   </sheetData>
@@ -1792,13 +1792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.47706601552773</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.28861081487083</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.2116200015935</v>
+        <v>17.01673386973482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.8174384769817</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.18124855162598</v>
       </c>
     </row>
   </sheetData>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.60073872321084</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.27139167645984</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.24701373639218</v>
+        <v>19.35792855106704</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.31249296771107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.99055509102438</v>
       </c>
     </row>
   </sheetData>
@@ -1892,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.7913896208435</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.3299700939179</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.21471513898427</v>
+        <v>24.2239458163876</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.55081219359229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.34493612428491</v>
       </c>
     </row>
   </sheetData>
@@ -1942,13 +1942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.68314677769287</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.50261368260747</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.24558922917432</v>
+        <v>18.36237943214339</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.16960557319831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.11972506930656</v>
       </c>
     </row>
   </sheetData>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.51219417488901</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.55618956330333</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.99265873549361</v>
+        <v>20.66763422392294</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.86826931621442</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.37803937486931</v>
       </c>
     </row>
   </sheetData>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.85108209863836</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.27559942931564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.07366528782238</v>
+        <v>16.96726892414768</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.66297079486515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.1527686794008</v>
       </c>
     </row>
   </sheetData>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.88714808285309</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.3746731971448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.31931822536041</v>
+        <v>18.18162390218386</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.95708601611238</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.45387001258018</v>
       </c>
     </row>
   </sheetData>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.43708233264429</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.05286004466709</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.26588801193076</v>
+        <v>23.26752843983038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.24048573039883</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.75312534988734</v>
       </c>
     </row>
   </sheetData>
@@ -2192,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.48623081142422</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.44742128998976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.02300714629679</v>
+        <v>17.84431431482252</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.54798859020195</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.26725262597428</v>
       </c>
     </row>
   </sheetData>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.65089628343836</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.2988526102226</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.01057220018551</v>
+        <v>18.84525695677398</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.67107707334098</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.7143481380865</v>
       </c>
     </row>
   </sheetData>
@@ -2292,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.38356471319422</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.51512223292893</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.61565443989069</v>
+        <v>20.4960684236918</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.23541065976606</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.03055885197515</v>
       </c>
     </row>
   </sheetData>
@@ -2342,13 +2342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.91266759453027</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.07682335714456</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.06460456113445</v>
+        <v>21.03064761734976</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.53773504869014</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.35774893878314</v>
       </c>
     </row>
   </sheetData>
@@ -2392,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.38942990319748</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.8638766280949</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.18020754900619</v>
+        <v>18.04923218172918</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.58220908348681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.4220985801221</v>
       </c>
     </row>
   </sheetData>
@@ -2442,13 +2442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.73758140049727</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.3232448322464</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.11013044379186</v>
+        <v>24.28972647555591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.69922851744026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.0008348296275</v>
       </c>
     </row>
   </sheetData>
@@ -2492,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.2128587973432</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.57939289796248</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.16239228194458</v>
+        <v>22.55853050258136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.41092890222228</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.94442719339446</v>
       </c>
     </row>
   </sheetData>
@@ -2542,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.47421279510973</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.02968778100254</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.89155446459784</v>
+        <v>17.60945751088596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.32067561318122</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.05147762855179</v>
       </c>
     </row>
   </sheetData>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.40226771707079</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.70307980510227</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.66279798284786</v>
+        <v>21.93810178754653</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.1095825082112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.3682075680291</v>
       </c>
     </row>
   </sheetData>
@@ -2642,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.28637011833866</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.74720521016359</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.81471380407578</v>
+        <v>27.56530696363423</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.07694282193201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.53411982175519</v>
       </c>
     </row>
   </sheetData>
@@ -2692,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.88776765915236</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.49964786145236</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.24014692337992</v>
+        <v>21.52211984497083</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.28280234623452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.76629188101584</v>
       </c>
     </row>
   </sheetData>
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.39907144822501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.50612737473913</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.16796841424725</v>
+        <v>17.46034682890849</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.60554217859026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.98149279079415</v>
       </c>
     </row>
   </sheetData>
@@ -2792,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.34852615044205</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.13435708484787</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.18871218837189</v>
+        <v>18.53680663608451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.74544848633752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.75822445402864</v>
       </c>
     </row>
   </sheetData>
@@ -2842,13 +2842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.83245405379334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.97945227192306</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.51736735331372</v>
+        <v>19.2940129397504</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.64869206841396</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.8743329883888</v>
       </c>
     </row>
   </sheetData>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.49208964467499</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.69487777450192</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.16829767631</v>
+        <v>22.21513953173164</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.93157141700065</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.6516858948799</v>
       </c>
     </row>
   </sheetData>
@@ -2942,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.76255573994925</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.12597904779533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.63882050103252</v>
+        <v>23.44842184716863</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.83626362360605</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.09901392416693</v>
       </c>
     </row>
   </sheetData>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.50792929804735</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.56090814074126</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.05123574494049</v>
+        <v>21.44368546130463</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.64757763601472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.34637650316832</v>
       </c>
     </row>
   </sheetData>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.82185198641799</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.45356521778755</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.14569030314443</v>
+        <v>18.77913605293671</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.21072179144486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.23468491661599</v>
       </c>
     </row>
   </sheetData>
@@ -3092,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.35928984903407</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.02315334752287</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.25320794296617</v>
+        <v>20.44824756527308</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.06603952781633</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.46820076819491</v>
       </c>
     </row>
   </sheetData>
@@ -3142,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36249066635673</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.17845929038437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.27195059099135</v>
+        <v>24.67400624811153</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.25441735472043</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.19901060495442</v>
       </c>
     </row>
   </sheetData>
@@ -3192,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.11315560430765</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.97538476397806</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.09639958000476</v>
+        <v>19.42419684833695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.49968257719637</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.68903518870193</v>
       </c>
     </row>
   </sheetData>
@@ -3242,13 +3242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.65332856638072</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.39452266423224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.10000780110029</v>
+        <v>22.56350172914719</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.65842080856426</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.29690277105238</v>
       </c>
     </row>
   </sheetData>
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.60450654482359</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.44614569500601</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.33226320323581</v>
+        <v>26.38924339996366</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.87212579371048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.32023853023544</v>
       </c>
     </row>
   </sheetData>
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.01300601691825</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.03125433942662</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.09045388810773</v>
+        <v>18.97495078381741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.70177778707464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.43744951583382</v>
       </c>
     </row>
   </sheetData>
@@ -3392,13 +3392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.10950253953569</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.45066786094034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.27100603342128</v>
+        <v>21.45951752837786</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.36632642536232</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.33486288084147</v>
       </c>
     </row>
   </sheetData>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.56034650020127</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.10616802428082</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.25348224944623</v>
+        <v>21.61401862046718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.81523692648469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.03448740188119</v>
       </c>
     </row>
   </sheetData>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.11682829806787</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.67085907026237</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.18019819141083</v>
+        <v>21.78576351593854</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.84171749391091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.26650178912314</v>
       </c>
     </row>
   </sheetData>
@@ -3542,13 +3542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.16867610584845</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.38817985507696</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.90536206485579</v>
+        <v>18.70378426499574</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.33691600641928</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.92050925999973</v>
       </c>
     </row>
   </sheetData>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.78181720298786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.51931039420756</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.65258877952407</v>
+        <v>24.59278774499576</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.01106510086587</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.48058920248519</v>
       </c>
     </row>
   </sheetData>
@@ -3642,13 +3642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.81486158842916</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.96337093073547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.90002831589453</v>
+        <v>19.09043854554242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.65066325482727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.69680900840887</v>
       </c>
     </row>
   </sheetData>
@@ -3692,13 +3692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.72840043137299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.52809279424521</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.21038940359906</v>
+        <v>17.95762717997647</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.04982844017348</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.35274147293192</v>
       </c>
     </row>
   </sheetData>
@@ -3742,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.50751996098155</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.56520798349186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.86326155415856</v>
+        <v>25.95714499704781</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.49177886352149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.57004287111903</v>
       </c>
     </row>
   </sheetData>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23827679979077</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.05833964633681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.4099823976256</v>
+        <v>19.86555036188364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.22678807547425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.95501092626606</v>
       </c>
     </row>
   </sheetData>
@@ -3842,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.44709796890797</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.46436981860043</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.78542138480404</v>
+        <v>18.04056905986402</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.80942286365754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.82476002183327</v>
       </c>
     </row>
   </sheetData>
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.6431699663916</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.51028743174671</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.96385201170354</v>
+        <v>26.12965443959055</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.68987863851615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.18049672029077</v>
       </c>
     </row>
   </sheetData>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.70960377274469</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.07977657038514</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.66796275147769</v>
+        <v>20.43309257549689</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.85728492283579</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.94411464425751</v>
       </c>
     </row>
   </sheetData>
@@ -3992,13 +3992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.24307721477866</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.27650116974506</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.48792945898501</v>
+        <v>21.88780055260479</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.61431295232833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.62917276761532</v>
       </c>
     </row>
   </sheetData>
@@ -4042,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.16314442815045</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.09106977120194</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.51164489422285</v>
+        <v>23.19345823408132</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.01998184054873</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.53147106132513</v>
       </c>
     </row>
   </sheetData>
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.29672913987452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.10248317403946</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.06206430926031</v>
+        <v>21.89661343526062</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.82587469951517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.33598720322962</v>
       </c>
     </row>
   </sheetData>
@@ -4142,13 +4142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.76785585863886</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.63220132299359</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.65505720630234</v>
+        <v>17.39917315918827</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.40593679079122</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.96034224713489</v>
       </c>
     </row>
   </sheetData>
@@ -4192,13 +4192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.92861638304133</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.33902582272414</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.03338844526447</v>
+        <v>25.11006877200602</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.16085722352696</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.58758017280402</v>
       </c>
     </row>
   </sheetData>
@@ -4242,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.21721734674357</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.2649047324988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.20759099737668</v>
+        <v>25.48667929589364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.62135186967467</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.55624081572758</v>
       </c>
     </row>
   </sheetData>
@@ -4292,13 +4292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.35514890049568</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.12565233452127</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.06006323436851</v>
+        <v>17.71459838547401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.4647105091812</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.43926113029865</v>
       </c>
     </row>
   </sheetData>
@@ -4342,13 +4342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.60686143160655</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.51907063042826</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.34738853360872</v>
+        <v>24.10721392847265</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.83685840374489</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.83987801412736</v>
       </c>
     </row>
   </sheetData>
@@ -4392,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.32342932954371</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.16913342824716</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.53996875150363</v>
+        <v>17.66463894181173</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.57685998188458</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.81680705904997</v>
       </c>
     </row>
   </sheetData>
@@ -4442,13 +4442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.5591942445246</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.01324829392547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.46976369998896</v>
+        <v>20.37036866718558</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.36657809970418</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.97073517205835</v>
       </c>
     </row>
   </sheetData>
@@ -4492,13 +4492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.99540148718498</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.33892089153401</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.02228707559464</v>
+        <v>19.64217312134599</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.15050009551107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.41628398078555</v>
       </c>
     </row>
   </sheetData>
@@ -4542,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.16421665220624</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.54319563423561</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.88038706960233</v>
+        <v>18.46417736837623</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.39660537499277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.03445878636449</v>
       </c>
     </row>
   </sheetData>
@@ -4592,13 +4592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.56667881478189</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.37864292838509</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.91602179128753</v>
+        <v>19.98976700609475</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.20008758923888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.42524613516096</v>
       </c>
     </row>
   </sheetData>
@@ -4642,13 +4642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.90394395046667</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.3485669632909</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.97677489574351</v>
+        <v>23.10992471444893</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.05508978484108</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.23248460090994</v>
       </c>
     </row>
   </sheetData>
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.66754427951156</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.75663138182476</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.42645840768514</v>
+        <v>17.46915462406644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.95379913898936</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.13375779926783</v>
       </c>
     </row>
   </sheetData>
@@ -4742,13 +4742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.35357196555821</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.46994256603974</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.59882797484341</v>
+        <v>17.52942255752297</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.30690801522296</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.80614039903159</v>
       </c>
     </row>
   </sheetData>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.95780701726897</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.94523872153529</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.14922320741784</v>
+        <v>20.23089785848449</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.25953254286247</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.3139648425288</v>
       </c>
     </row>
   </sheetData>
@@ -4842,13 +4842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.08930568980784</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.72775465338477</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.93695079176249</v>
+        <v>19.65296630676276</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.82078466099746</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.98632317929748</v>
       </c>
     </row>
   </sheetData>
@@ -4892,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.51411787789205</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.35614157110785</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.00526830028424</v>
+        <v>16.82653769831421</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.87206693484615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.02011183374253</v>
       </c>
     </row>
   </sheetData>
@@ -4942,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.72334917117123</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.1603842548346</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.14882280839786</v>
+        <v>19.29222156632604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.30070275939532</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.20540390496978</v>
       </c>
     </row>
   </sheetData>
@@ -4992,13 +4992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.53046519816744</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.81228479994825</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.05342748917449</v>
+        <v>21.08662873429117</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.40943466620548</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.03473823191349</v>
       </c>
     </row>
   </sheetData>
@@ -5042,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.72530962866869</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.92471675415169</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.95746773394413</v>
+        <v>21.08293322265116</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.34921088436774</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.82349168349402</v>
       </c>
     </row>
   </sheetData>
@@ -5092,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.44879892648938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.89288689695061</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.36112985337611</v>
+        <v>20.94534080430794</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.01910530982525</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.40213381312288</v>
       </c>
     </row>
   </sheetData>
@@ -5142,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.08936745703356</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.09724960237404</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.33440173777834</v>
+        <v>23.53226140620225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.47564391849057</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.95407811925394</v>
       </c>
     </row>
   </sheetData>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.59991587282883</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.40115808607575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.83606840785914</v>
+        <v>20.34503044839576</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.48783387451727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.00435668521073</v>
       </c>
     </row>
   </sheetData>
@@ -5242,13 +5242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.365224356249</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.76350061281807</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.16523163495244</v>
+        <v>28.22371001144482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.30825980163042</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.02553249598864</v>
       </c>
     </row>
   </sheetData>
@@ -5292,13 +5292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.35032851819323</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.90277169251232</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.46477452280219</v>
+        <v>25.04495445710794</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.58057258557525</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.05856026591663</v>
       </c>
     </row>
   </sheetData>
@@ -5342,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.23027865296353</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.7421088926628</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.9603607497911</v>
+        <v>17.66663558099425</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.54891749466491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.06732360608257</v>
       </c>
     </row>
   </sheetData>
@@ -5392,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.96145640040172</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.76943830231313</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.91733380173432</v>
+        <v>24.24888203116561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.19810499304619</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.38344574496609</v>
       </c>
     </row>
   </sheetData>
@@ -5442,13 +5442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.91515971286996</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.80421112538723</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.93070357990063</v>
+        <v>18.46570689182171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.65117900570561</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.04917088201739</v>
       </c>
     </row>
   </sheetData>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.98392499894932</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.32626151083153</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.58795806587868</v>
+        <v>19.92601510738172</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.44351918225734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.59148135795107</v>
       </c>
     </row>
   </sheetData>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.00592971409452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.38405803620814</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.61096594601325</v>
+        <v>15.01984041894128</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.38564489160334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.63962374991276</v>
       </c>
     </row>
   </sheetData>
@@ -5592,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.49627078124718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.05616125683886</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.12179594359247</v>
+        <v>19.09725991842349</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.93174728731705</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.26424897254456</v>
       </c>
     </row>
   </sheetData>
@@ -5642,13 +5642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.96200971413042</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.42204574082663</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.36798292818193</v>
+        <v>20.84295014760078</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.03555686430801</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.63422654388857</v>
       </c>
     </row>
   </sheetData>
@@ -5692,13 +5692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.16508413371342</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.37565127747876</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.73173341065887</v>
+        <v>18.64945107435115</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.27915193956834</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.32396498749132</v>
       </c>
     </row>
   </sheetData>
@@ -5742,13 +5742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.74156170017256</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.40810529695036</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.13383907545784</v>
+        <v>27.0406073121578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.94975666181343</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.02191474453594</v>
       </c>
     </row>
   </sheetData>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.7319921486092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.75497357713646</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.80670254293761</v>
+        <v>20.40605762319537</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.92996309106335</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.60168846847741</v>
       </c>
     </row>
   </sheetData>
@@ -5842,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.26387083587054</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.42957198323728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.78581530708589</v>
+        <v>23.38843646099876</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.78363088913962</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.02019371952326</v>
       </c>
     </row>
   </sheetData>
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.66950059609909</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.24665346441451</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.61338458094249</v>
+        <v>19.55565588957053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.14077562863837</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.74612780356495</v>
       </c>
     </row>
   </sheetData>
@@ -5942,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.18894283653658</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.59829517877377</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.83901740948378</v>
+        <v>21.17620922403452</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.28789258549509</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.32427967948009</v>
       </c>
     </row>
   </sheetData>
@@ -5992,13 +5992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.89687520461042</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.92207285015577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.40164678664153</v>
+        <v>22.66886471237598</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.06340196907843</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.12555933899128</v>
       </c>
     </row>
   </sheetData>
@@ -6042,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.3033819872751</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.12200583434516</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.31541512936245</v>
+        <v>19.91115381182585</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.16737389765959</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.39560617858803</v>
       </c>
     </row>
   </sheetData>
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.51012064687713</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.54864203465145</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.55177695836077</v>
+        <v>21.06612497760953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.78407569922085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.29327798531081</v>
       </c>
     </row>
   </sheetData>
@@ -6142,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.73542259605647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.02873157160182</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.61250101910888</v>
+        <v>20.48746463560197</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.74898489203786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.30565869139773</v>
       </c>
     </row>
   </sheetData>
@@ -6192,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.30342772203808</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.74727492486978</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.82021569350095</v>
+        <v>19.24155392424957</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.40974046472162</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.82797950661754</v>
       </c>
     </row>
   </sheetData>
@@ -6242,13 +6242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.10644669197459</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.55376150661147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.86617287622672</v>
+        <v>20.58177237052604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.99908600977782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.72665728864947</v>
       </c>
     </row>
   </sheetData>
@@ -6292,13 +6292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.18284904144188</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.99423351795378</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.16679070606248</v>
+        <v>20.27802515671529</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.77966195651588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.17631635820415</v>
       </c>
     </row>
   </sheetData>
@@ -6342,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.73046144614133</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.63382891395111</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.33820969303554</v>
+        <v>18.62772510257654</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.92805852174351</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.65677825840124</v>
       </c>
     </row>
   </sheetData>
@@ -6392,13 +6392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.3627033632728</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.004895322379</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.72407711382724</v>
+        <v>21.38189006707753</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.69369126550865</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.91068149946699</v>
       </c>
     </row>
   </sheetData>
@@ -6442,13 +6442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.79507881987436</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.19671378589848</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.38220775350576</v>
+        <v>26.60678069661711</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.54332217333995</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.93568833758394</v>
       </c>
     </row>
   </sheetData>
@@ -6492,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.76841337618588</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.53762415848485</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.80464872185</v>
+        <v>18.41718430835575</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.56309181115533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.08190724062183</v>
       </c>
     </row>
   </sheetData>
@@ -6542,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.36409315943309</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.22260658815705</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.504430844352</v>
+        <v>23.83125307314965</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.16743748877002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.11206678451535</v>
       </c>
     </row>
   </sheetData>
@@ -6592,13 +6592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.73709440112171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.46585622441958</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.45405431776026</v>
+        <v>18.18907795791355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.77131087987802</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.8793532604307</v>
       </c>
     </row>
   </sheetData>
@@ -6642,13 +6642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.36161543482292</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.55538588699985</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.95135202461562</v>
+        <v>19.09380813554425</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.79570934592626</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.01955653999554</v>
       </c>
     </row>
   </sheetData>
@@ -6692,13 +6692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.68594914332985</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.66583229265814</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.23523472768553</v>
+        <v>19.41224520689848</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.25116742027149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.88312141531705</v>
       </c>
     </row>
   </sheetData>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.5561549572117</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.89178443298761</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.24369904216454</v>
+        <v>24.68784387467281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.75390799768533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.98078268758019</v>
       </c>
     </row>
   </sheetData>
@@ -6792,13 +6792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.09336523027877</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.44347564769833</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.43817997951325</v>
+        <v>17.18431213850956</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.51740573049687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.96653534826413</v>
       </c>
     </row>
   </sheetData>
@@ -6842,13 +6842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.51865683167107</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.21012425816123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.86712765528775</v>
+        <v>17.55713479095029</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.06127557399018</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.32151155392437</v>
       </c>
     </row>
   </sheetData>
@@ -6892,13 +6892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.19786730914388</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.35720854554034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.24890064294239</v>
+        <v>23.34200399542806</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.24337888961653</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.49706292892946</v>
       </c>
     </row>
   </sheetData>
@@ -6942,13 +6942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.83109521973631</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.7001158800176</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.76235843536793</v>
+        <v>24.43295370025422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.41979438786607</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.00315721555533</v>
       </c>
     </row>
   </sheetData>
@@ -6992,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.18462406011791</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.0314249423125</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.28223327493148</v>
+        <v>20.62977953255601</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.58455522662432</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.58903050328047</v>
       </c>
     </row>
   </sheetData>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.59033415949766</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.71870056200471</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.42537312891573</v>
+        <v>18.00028347019328</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.77899459391184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.54155314419611</v>
       </c>
     </row>
   </sheetData>
@@ -7092,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.08819942028322</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.21818581850279</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.48246096844848</v>
+        <v>23.17802364351613</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.38711327355556</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.19849653103963</v>
       </c>
     </row>
   </sheetData>
@@ -7142,13 +7142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.46467884556073</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.49285399184575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.91356735605867</v>
+        <v>20.79020874858181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.8763360123302</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.64035060647061</v>
       </c>
     </row>
   </sheetData>
@@ -7192,13 +7192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.72820946207831</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.39373315630642</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.96988614234165</v>
+        <v>27.08914176863005</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.37536957006883</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.82014602978568</v>
       </c>
     </row>
   </sheetData>
@@ -7242,13 +7242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.02873957021466</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.02555919909036</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.26382315236719</v>
+        <v>16.50819186112292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.1147385442997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.82861033866125</v>
       </c>
     </row>
   </sheetData>
@@ -7292,13 +7292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.09233683455439</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.31150677800116</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.75123076796193</v>
+        <v>18.31859281339443</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.97847481156325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.18137927754114</v>
       </c>
     </row>
   </sheetData>
@@ -7342,13 +7342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.5158152082277</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.66360494812411</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.66324170784545</v>
+        <v>18.77941406791779</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.52206043808184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.95964305554565</v>
       </c>
     </row>
   </sheetData>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.0584939024926</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.35444921213853</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.11694880539275</v>
+        <v>19.03613492298344</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.09340601966469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.28311098889188</v>
       </c>
     </row>
   </sheetData>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.63967678766439</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.82531353979533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.82291581988652</v>
+        <v>19.66631609568426</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.65139887119922</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.29792174903632</v>
       </c>
     </row>
   </sheetData>
@@ -7492,13 +7492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.93420023043948</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.42588183446052</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.74906889408186</v>
+        <v>25.18832532498334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.90275421371634</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.95390249283485</v>
       </c>
     </row>
   </sheetData>
@@ -7542,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.20261186501354</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.14544515404483</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.99909049638405</v>
+        <v>18.70660802613432</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.00601856624995</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.81095810709999</v>
       </c>
     </row>
   </sheetData>
@@ -7592,13 +7592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.31408521150264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.74857485092133</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.46365827390901</v>
+        <v>19.75702876948419</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.87278501153757</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.64176263604087</v>
       </c>
     </row>
   </sheetData>
@@ -7642,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.48298721658237</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.48723125014835</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.63482475115923</v>
+        <v>17.84152113986404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.34289646445907</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.95630343627347</v>
       </c>
     </row>
   </sheetData>
@@ -7692,13 +7692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.30936555124739</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.57583508816865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.57179573450898</v>
+        <v>22.95190386296263</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.03646648117412</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.16618887121192</v>
       </c>
     </row>
   </sheetData>
@@ -7742,13 +7742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.44444623499762</v>
-      </c>
-      <c r="C2" t="n">
-        <v>14.72508936698066</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.56507799369945</v>
+        <v>22.29402241911286</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.37772070289979</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.40437097393082</v>
       </c>
     </row>
   </sheetData>
@@ -7792,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.80376976506528</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.28530311718316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.89293458115825</v>
+        <v>20.91677459011696</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.07253230133967</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.27665842713071</v>
       </c>
     </row>
   </sheetData>
@@ -7842,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.48301289385104</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.74498640744289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.8763521633646</v>
+        <v>18.68018129430926</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.15350299599178</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.35961616743013</v>
       </c>
     </row>
   </sheetData>
@@ -7892,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.41283845361352</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.19408264457036</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.82843435702108</v>
+        <v>19.30745360618821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.37457067521473</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.67752134413266</v>
       </c>
     </row>
   </sheetData>
@@ -7942,13 +7942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.63096648943837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.00951367632715</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.80709433394701</v>
+        <v>21.51509759740698</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.76286640388281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.53970882707786</v>
       </c>
     </row>
   </sheetData>
@@ -7992,13 +7992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.72789121480131</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.43123302338133</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.13102207162143</v>
+        <v>23.28853968204374</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.93363333678308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.23540915360813</v>
       </c>
     </row>
   </sheetData>
@@ -8042,13 +8042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.74105527828652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.44625850581516</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.11991682367882</v>
+        <v>18.16912604203361</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.3159966302766</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.1668152256101</v>
       </c>
     </row>
   </sheetData>
@@ -8092,13 +8092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.21417997639984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.18885931603759</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.13508689317036</v>
+        <v>23.89008305338607</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.49912625448871</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.18652893867061</v>
       </c>
     </row>
   </sheetData>
@@ -8142,13 +8142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.85112949119004</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.18947409781581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.22631181383436</v>
+        <v>17.37846082251379</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.71377037648277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.87420352611479</v>
       </c>
     </row>
   </sheetData>
@@ -8192,13 +8192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38104537083225</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.98067585593383</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.84749629893379</v>
+        <v>20.25185761575083</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.35049349526711</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.6219900656521</v>
       </c>
     </row>
   </sheetData>
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.45377456929072</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.73563844310345</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.54969679118632</v>
+        <v>20.21821691838957</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.71718358992914</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.89571416088433</v>
       </c>
     </row>
   </sheetData>
@@ -8292,13 +8292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.23177184723438</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.10611132045815</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.47871035805099</v>
+        <v>22.29837340125731</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.49059768713598</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.35944855206496</v>
       </c>
     </row>
   </sheetData>
@@ -8342,13 +8342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.38179911030743</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.66495564060308</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.99594790066578</v>
+        <v>19.21792560191299</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.35094727281337</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.21331301752042</v>
       </c>
     </row>
   </sheetData>
@@ -8392,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.53217106917584</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.48556389160781</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.65541377492025</v>
+        <v>17.86151915098231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.9970074638257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.73293450260856</v>
       </c>
     </row>
   </sheetData>
@@ -8442,13 +8442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.31648799767439</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.42366469142474</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.97558312765094</v>
+        <v>20.14618056291231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.81693738383894</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.42327277957905</v>
       </c>
     </row>
   </sheetData>
@@ -8492,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.54800191020548</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.50821452371563</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.44589819128782</v>
+        <v>20.03638439588645</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.04406901363239</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.02493243212789</v>
       </c>
     </row>
   </sheetData>
@@ -8542,13 +8542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.09998403884269</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.6176907987473</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.24183434186633</v>
+        <v>18.12426751951305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.52509684147509</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.95701549287211</v>
       </c>
     </row>
   </sheetData>
@@ -8592,13 +8592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.55081026534635</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.67428189442034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.16578442708409</v>
+        <v>25.77280973337545</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.18014623289976</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.00770230296507</v>
       </c>
     </row>
   </sheetData>
@@ -8642,13 +8642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.2483986105011</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.22553534250263</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.0840027573865</v>
+        <v>18.25813170776703</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.52205297098083</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.45073546548296</v>
       </c>
     </row>
   </sheetData>
@@ -8692,13 +8692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.59778752576444</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.37436081096494</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.94585207489834</v>
+        <v>18.66233939315821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.22774070395864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.11056433939066</v>
       </c>
     </row>
   </sheetData>
@@ -8742,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.41479618479542</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.62895040811953</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.80999478498221</v>
+        <v>25.50661027011892</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.20780342110491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.9157365519017</v>
       </c>
     </row>
   </sheetData>
@@ -8792,13 +8792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.27326067434666</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.19114899542105</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.99047438609009</v>
+        <v>23.1762330268907</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.14453951271887</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.62746829815487</v>
       </c>
     </row>
   </sheetData>
@@ -8842,13 +8842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28181491748935</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.15515937002354</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.84047147184727</v>
+        <v>21.69096377632725</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.66494523807498</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.86329606015087</v>
       </c>
     </row>
   </sheetData>
@@ -8892,13 +8892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.34995688551026</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.14012469620555</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.46911447740827</v>
+        <v>18.11550043174823</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.64422600398576</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.53135297231751</v>
       </c>
     </row>
   </sheetData>
@@ -8942,13 +8942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.5210218688459</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.86473352654489</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.58789417388856</v>
+        <v>18.66970596744362</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.97456535866329</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.03163031641209</v>
       </c>
     </row>
   </sheetData>
@@ -8992,13 +8992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.68295249732611</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.63393603831371</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.06107287516288</v>
+        <v>16.58427262952565</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.55329819149009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.26497684966367</v>
       </c>
     </row>
   </sheetData>
@@ -9042,13 +9042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.84782544686434</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.02548004348037</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.10951011919077</v>
+        <v>23.06250099608088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.92554791704165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.9926738737196</v>
       </c>
     </row>
   </sheetData>
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.52972175517225</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.0990395132652</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.3880081689548</v>
+        <v>18.83760979962302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.62709687454529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.28327243707647</v>
       </c>
     </row>
   </sheetData>
@@ -9142,13 +9142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.67933147653255</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.43614287874326</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.39433710558048</v>
+        <v>21.10402479677138</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.59130145641136</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.8080285758173</v>
       </c>
     </row>
   </sheetData>
@@ -9192,13 +9192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.69754471552891</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.64552167426959</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.78935038252293</v>
+        <v>21.42463739084916</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.93541736605686</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.56151607671166</v>
       </c>
     </row>
   </sheetData>
@@ -9242,13 +9242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.26489675321843</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.57985330777584</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.03176076109498</v>
+        <v>18.79764675002102</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.95641604890854</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.79091350696433</v>
       </c>
     </row>
   </sheetData>
@@ -9292,13 +9292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.19626924792643</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.28479094499445</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.36574290656381</v>
+        <v>19.1249071308066</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.73819955878229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.41376309662715</v>
       </c>
     </row>
   </sheetData>
@@ -9342,13 +9342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.33736347570808</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.54918890534846</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.18772591181732</v>
+        <v>25.43892505626168</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.99669221316107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.917619185075</v>
       </c>
     </row>
   </sheetData>
@@ -9392,13 +9392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.9389787971248</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.73089945971169</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.20937779766537</v>
+        <v>20.2806696055982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.92808438009735</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.43412090033671</v>
       </c>
     </row>
   </sheetData>
@@ -9442,13 +9442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.7418260192681</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.32429950891461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.01733733796842</v>
+        <v>19.81640902718211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.07964143137731</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.39615432765479</v>
       </c>
     </row>
   </sheetData>
@@ -9492,13 +9492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.8860294616693</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.19747246501421</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.34763683850856</v>
+        <v>19.11819776680957</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.03256780024597</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.42829991285216</v>
       </c>
     </row>
   </sheetData>
@@ -9542,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.50706509316328</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.07496309434811</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.9276127037743</v>
+        <v>23.52453813473173</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.09817817358969</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.15320831555184</v>
       </c>
     </row>
   </sheetData>
@@ -9592,13 +9592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.34099072701799</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.97340887382689</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.02904506321394</v>
+        <v>23.33765225921457</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.43306539009231</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.82376765587544</v>
       </c>
     </row>
   </sheetData>
@@ -9642,13 +9642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.09400056627361</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.70812154956989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.61081746460752</v>
+        <v>24.37806611636798</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.77820724034018</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.04964443811878</v>
       </c>
     </row>
   </sheetData>
@@ -9692,13 +9692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.11342624035067</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.26382834209543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.70826548087035</v>
+        <v>19.84890446384956</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.85092134745066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.15515722788284</v>
       </c>
     </row>
   </sheetData>
@@ -9742,13 +9742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.06563614235044</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.90653217318517</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.59606749980162</v>
+        <v>23.82800750387396</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14.62332098003935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.64465044642884</v>
       </c>
     </row>
   </sheetData>
@@ -9792,13 +9792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.42152263214249</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.55693696388679</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.01330275620741</v>
+        <v>18.49621260240595</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.42400718646268</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.12703835232413</v>
       </c>
     </row>
   </sheetData>
@@ -9842,13 +9842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.42435880207744</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.72165141640378</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.83767745142251</v>
+        <v>15.80455647861453</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.21338820770614</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.83827318697061</v>
       </c>
     </row>
   </sheetData>
@@ -9892,13 +9892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.84398245318509</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.29407563412094</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.57668991263499</v>
+        <v>20.07385424992928</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.10887600299875</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.61696758660021</v>
       </c>
     </row>
   </sheetData>
@@ -9942,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.66631015348404</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.6384864383167</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.57934080228413</v>
+        <v>20.62993308642147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.45801806132866</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.08342917639991</v>
       </c>
     </row>
   </sheetData>
@@ -9992,13 +9992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.1239665255933</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.0523497940352</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.52347173764035</v>
+        <v>18.2720850891397</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.35699832048771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.44722938413592</v>
       </c>
     </row>
   </sheetData>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.19045131334382</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.62303454831343</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.3128298121612</v>
+        <v>27.92429675082286</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.87960552515594</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.04593619715587</v>
       </c>
     </row>
   </sheetData>
@@ -10092,13 +10092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.22876797487366</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.51731919955206</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.72295077630572</v>
+        <v>15.73342097094839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.08841397550784</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.41844528522946</v>
       </c>
     </row>
   </sheetData>
@@ -10142,13 +10142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.86620065900053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.90255424595032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.31809846423743</v>
+        <v>19.84758656484168</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.07550475109457</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.89490821521093</v>
       </c>
     </row>
   </sheetData>
@@ -10192,13 +10192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.88923641155149</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.21582042403217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.837142057713</v>
+        <v>22.79480311036295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.50578046485725</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.99128259366315</v>
       </c>
     </row>
   </sheetData>
@@ -10242,13 +10242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.32090985244281</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.39087562166305</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.94426079636484</v>
+        <v>29.31804506045219</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.05785198720015</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.28669305715586</v>
       </c>
     </row>
   </sheetData>
@@ -10292,13 +10292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.26761709478797</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.20935177031887</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.72025875118634</v>
+        <v>23.5524929718785</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.55037960398354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.3299765695464</v>
       </c>
     </row>
   </sheetData>
@@ -10342,13 +10342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.08560210945038</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.54826840546856</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.00204866005659</v>
+        <v>25.07761843202305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.25643493319888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.92810899418152</v>
       </c>
     </row>
   </sheetData>
@@ -10392,13 +10392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.35578882568737</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.21262916305475</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.66138218525813</v>
+        <v>20.9209002158592</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.59498679868985</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.86973123670533</v>
       </c>
     </row>
   </sheetData>
@@ -10442,13 +10442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.55789517621375</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.54559375512889</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.54184933434984</v>
+        <v>17.67157627765875</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.60344025671011</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.18267858437782</v>
       </c>
     </row>
   </sheetData>
@@ -10492,13 +10492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.36494038365652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.50287728926058</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.54803388066104</v>
+        <v>19.2016680142622</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.87517254994919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.70925150658866</v>
       </c>
     </row>
   </sheetData>
@@ -10542,13 +10542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.49429460422881</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.13221870645768</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.02552280324668</v>
+        <v>21.09968604794853</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.76703432479522</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.58675441082478</v>
       </c>
     </row>
   </sheetData>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.24401865451406</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.91952642465924</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.44538793508013</v>
+        <v>19.2250740395055</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.1355855227999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.65681116674646</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.41193106929261</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.91719270494497</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.38695220645081</v>
+        <v>23.64103204269862</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.32770884558207</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.19581888939037</v>
       </c>
     </row>
   </sheetData>
@@ -692,13 +692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.39072429262812</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.80591307656732</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.46639778637776</v>
+        <v>22.97973729979146</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.41068130381903</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.75205368823216</v>
       </c>
     </row>
   </sheetData>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.70876144890668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.97895144161064</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.72146366470049</v>
+        <v>22.82169145101596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.0339198253313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.95240758627691</v>
       </c>
     </row>
   </sheetData>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.02275075691368</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.05873015190059</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.41589139084699</v>
+        <v>23.854442257629</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.38340559141754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.61925265287237</v>
       </c>
     </row>
   </sheetData>
@@ -842,13 +842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.94684013011025</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.34615271942581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.18051770559967</v>
+        <v>25.25208689237936</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.57896788671048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.49935240416131</v>
       </c>
     </row>
   </sheetData>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.94277236700007</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.99032621931648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.77628524231944</v>
+        <v>25.6845888077111</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.58990888240357</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.58106244610656</v>
       </c>
     </row>
   </sheetData>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.00414374952524</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.74809059079432</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.27623621817886</v>
+        <v>24.8676495117445</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.39377827629709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.01593288946357</v>
       </c>
     </row>
   </sheetData>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.85263283285062</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.71522447067131</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.02287896797837</v>
+        <v>22.19692976026963</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.41724808104154</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.70699467578396</v>
       </c>
     </row>
   </sheetData>
@@ -1042,13 +1042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.32186374844024</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.52009816276944</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.53639908356001</v>
+        <v>25.85150102474123</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.58376772168886</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.00420972337052</v>
       </c>
     </row>
   </sheetData>
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.89679877881625</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.6111879265847</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.86948854289238</v>
+        <v>22.49071941979321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.86866598380101</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.32580178644695</v>
       </c>
     </row>
   </sheetData>
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.09172828864536</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.23560367117592</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.77713900525124</v>
+        <v>26.44015088523781</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.76713177123338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.32002919724178</v>
       </c>
     </row>
   </sheetData>
@@ -1192,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.63872172453603</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.92436533772203</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.35519913774049</v>
+        <v>21.71359947471112</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.4335603644821</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.33324864381319</v>
       </c>
     </row>
   </sheetData>
@@ -1242,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.5667437839385</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.8241733514425</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.31932335656823</v>
+        <v>23.95781178522795</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.6010832853465</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.54191019484806</v>
       </c>
     </row>
   </sheetData>
@@ -1292,13 +1292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.13707272973053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.36294012461794</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.92926155460204</v>
+        <v>23.09185808794813</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.46893953259602</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.77789309886255</v>
       </c>
     </row>
   </sheetData>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.86608600286051</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.95937457868608</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.50880334370353</v>
+        <v>18.12440661312677</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.72832937324501</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.17864721046191</v>
       </c>
     </row>
   </sheetData>
@@ -1392,13 +1392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.39087685624306</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.71023904236861</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.70274452069858</v>
+        <v>20.26859886330015</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.37667804175968</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.25109672499974</v>
       </c>
     </row>
   </sheetData>
@@ -1442,13 +1442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.12540986683749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.61864735655447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.41602481016652</v>
+        <v>26.72925956221616</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.76557903938131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.5457631282333</v>
       </c>
     </row>
   </sheetData>
@@ -1492,13 +1492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.14081511655589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.06327408355864</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.33349672177718</v>
+        <v>19.22503705697857</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.63190323401451</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.68065350459748</v>
       </c>
     </row>
   </sheetData>
@@ -1542,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.3145656909482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.58387320879106</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.80854328051056</v>
+        <v>23.03711307632866</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.31944073289067</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.28543573885249</v>
       </c>
     </row>
   </sheetData>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.15469932302922</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.83373157721208</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.50261960207982</v>
+        <v>20.26071495816451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.93271232433867</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.19130893584322</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.62973060989766</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.06890922811543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.16485171024601</v>
+        <v>23.93097752886727</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.29196736762799</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.90505933485348</v>
       </c>
     </row>
   </sheetData>
@@ -1692,13 +1692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.23954511386913</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.5742987017859</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.80343934708014</v>
+        <v>23.32058165421627</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.72082033700546</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.77416213369224</v>
       </c>
     </row>
   </sheetData>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.67656554860938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.99483071983768</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.62273893318902</v>
+        <v>23.99696283256572</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.39964325961213</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.04749861838455</v>
       </c>
     </row>
   </sheetData>
@@ -1792,13 +1792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.01673386973482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.8174384769817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.18124855162598</v>
+        <v>17.00690800610012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.00943873668482</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.82273619608103</v>
       </c>
     </row>
   </sheetData>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.35792855106704</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16.31249296771107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.99055509102438</v>
+        <v>19.00362382877133</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.43668196494016</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.20595856248094</v>
       </c>
     </row>
   </sheetData>
@@ -1892,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2239458163876</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.55081219359229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.34493612428491</v>
+        <v>23.82176848633267</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.12010854762355</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.35219887587114</v>
       </c>
     </row>
   </sheetData>
@@ -1942,13 +1942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.36237943214339</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.16960557319831</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.11972506930656</v>
+        <v>22.64121904058083</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.48481216785098</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.44417863095364</v>
       </c>
     </row>
   </sheetData>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.66763422392294</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.86826931621442</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.37803937486931</v>
+        <v>21.53660977298878</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.70898845194872</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.48956342946589</v>
       </c>
     </row>
   </sheetData>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.96726892414768</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.66297079486515</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.1527686794008</v>
+        <v>24.43980504126761</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.74334604291153</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.12908691606795</v>
       </c>
     </row>
   </sheetData>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.18162390218386</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.95708601611238</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.45387001258018</v>
+        <v>22.7283672599312</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.61893657399583</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.00241350103548</v>
       </c>
     </row>
   </sheetData>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.26752843983038</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.24048573039883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.75312534988734</v>
+        <v>17.23958737548176</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.21289069244371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.53410543975765</v>
       </c>
     </row>
   </sheetData>
@@ -2192,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.84431431482252</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.54798859020195</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.26725262597428</v>
+        <v>22.44167593215422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.32327398881395</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.49026461224138</v>
       </c>
     </row>
   </sheetData>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.84525695677398</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.67107707334098</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.7143481380865</v>
+        <v>24.00467272608157</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.85341530390193</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.16703660709225</v>
       </c>
     </row>
   </sheetData>
@@ -2292,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.4960684236918</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.23541065976606</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.03055885197515</v>
+        <v>20.01400917414371</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.99959919804079</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.16234234522119</v>
       </c>
     </row>
   </sheetData>
@@ -2342,13 +2342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.03064761734976</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.53773504869014</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.35774893878314</v>
+        <v>31.00813685680638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.89034747128728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.92497855028857</v>
       </c>
     </row>
   </sheetData>
@@ -2392,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.04923218172918</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.58220908348681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.4220985801221</v>
+        <v>23.58144867987633</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.44869518576309</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.32996618757024</v>
       </c>
     </row>
   </sheetData>
@@ -2442,13 +2442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.28972647555591</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.69922851744026</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.0008348296275</v>
+        <v>23.70448424144136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.54304874123774</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.36923395224741</v>
       </c>
     </row>
   </sheetData>
@@ -2492,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.55853050258136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15.41092890222228</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.94442719339446</v>
+        <v>23.44316721699594</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.73871443006633</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.50247926068318</v>
       </c>
     </row>
   </sheetData>
@@ -2542,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.60945751088596</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.32067561318122</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.05147762855179</v>
+        <v>18.29438440335812</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.48285609942741</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.51111992693652</v>
       </c>
     </row>
   </sheetData>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.93810178754653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.1095825082112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.3682075680291</v>
+        <v>24.16693846347719</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.37056867142981</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.74582672860199</v>
       </c>
     </row>
   </sheetData>
@@ -2642,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.56530696363423</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.07694282193201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.53411982175519</v>
+        <v>23.94620636842889</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.07038570036697</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.8929028720342</v>
       </c>
     </row>
   </sheetData>
@@ -2692,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.52211984497083</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.28280234623452</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.76629188101584</v>
+        <v>22.6241729521713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.01732388298612</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.41492440001789</v>
       </c>
     </row>
   </sheetData>
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.46034682890849</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.60554217859026</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.98149279079415</v>
+        <v>26.30288913991996</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.23856520435798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.88923695346757</v>
       </c>
     </row>
   </sheetData>
@@ -2792,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.53680663608451</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.74544848633752</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.75822445402864</v>
+        <v>21.47371297763516</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.21677575474721</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.9611499803571</v>
       </c>
     </row>
   </sheetData>
@@ -2842,13 +2842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.2940129397504</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.64869206841396</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.8743329883888</v>
+        <v>21.29547104838864</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.40434558592638</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.74406579419999</v>
       </c>
     </row>
   </sheetData>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.21513953173164</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.93157141700065</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.6516858948799</v>
+        <v>25.64911993215144</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.13502423927772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.65145921281609</v>
       </c>
     </row>
   </sheetData>
@@ -2942,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.44842184716863</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15.83626362360605</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.09901392416693</v>
+        <v>26.49028674522171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.34322860765777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.62785719778926</v>
       </c>
     </row>
   </sheetData>
@@ -2992,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.44368546130463</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.64757763601472</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.34637650316832</v>
+        <v>21.08293170993564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.43867054878804</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.08146997404352</v>
       </c>
     </row>
   </sheetData>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.77913605293671</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.21072179144486</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.23468491661599</v>
+        <v>23.95464740487247</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.04669153026901</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.16792005625713</v>
       </c>
     </row>
   </sheetData>
@@ -3092,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.44824756527308</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.06603952781633</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.46820076819491</v>
+        <v>23.36884206987897</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.41024318523194</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.16525977376671</v>
       </c>
     </row>
   </sheetData>
@@ -3142,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.67400624811153</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.25441735472043</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.19901060495442</v>
+        <v>19.70736768510853</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.3013661143074</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.90385293497723</v>
       </c>
     </row>
   </sheetData>
@@ -3192,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.42419684833695</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.49968257719637</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.68903518870193</v>
+        <v>18.92828368850551</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.08007489335818</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.97338594379831</v>
       </c>
     </row>
   </sheetData>
@@ -3242,13 +3242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.56350172914719</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.65842080856426</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.29690277105238</v>
+        <v>24.45835471250613</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.69581678265173</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.78430656084829</v>
       </c>
     </row>
   </sheetData>
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.38924339996366</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.87212579371048</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.32023853023544</v>
+        <v>20.97781067849091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.29149978328979</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.73236538409041</v>
       </c>
     </row>
   </sheetData>
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.97495078381741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.70177778707464</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.43744951583382</v>
+        <v>23.84834849256025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.17211829893897</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.37892548757511</v>
       </c>
     </row>
   </sheetData>
@@ -3392,13 +3392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.45951752837786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.36632642536232</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.33486288084147</v>
+        <v>20.67796947271499</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.61318690962</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.61599713628874</v>
       </c>
     </row>
   </sheetData>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.61401862046718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.81523692648469</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.03448740188119</v>
+        <v>23.50463608638653</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.27889223747904</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.65057772937004</v>
       </c>
     </row>
   </sheetData>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.78576351593854</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.84171749391091</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.26650178912314</v>
+        <v>20.94585786238881</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.40175875217471</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.6213942860113</v>
       </c>
     </row>
   </sheetData>
@@ -3542,13 +3542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.70378426499574</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.33691600641928</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.92050925999973</v>
+        <v>20.39318549575411</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.69138661349771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.92132721690524</v>
       </c>
     </row>
   </sheetData>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.59278774499576</v>
-      </c>
-      <c r="C2" t="n">
-        <v>17.01106510086587</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.48058920248519</v>
+        <v>24.46351444699577</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.61502980472269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.03826553991425</v>
       </c>
     </row>
   </sheetData>
@@ -3642,13 +3642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.09043854554242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.65066325482727</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.69680900840887</v>
+        <v>16.95634991366065</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.65461887763937</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.39192306075109</v>
       </c>
     </row>
   </sheetData>
@@ -3692,13 +3692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.95762717997647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.04982844017348</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.35274147293192</v>
+        <v>17.80984645806292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.55269010630495</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.58477489044015</v>
       </c>
     </row>
   </sheetData>
@@ -3742,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.95714499704781</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.49177886352149</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.57004287111903</v>
+        <v>23.95202220583026</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.13542796502249</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.57520903953505</v>
       </c>
     </row>
   </sheetData>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.86555036188364</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.22678807547425</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.95501092626606</v>
+        <v>28.4105408764074</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.42135957468914</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.10494434276828</v>
       </c>
     </row>
   </sheetData>
@@ -3842,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.04056905986402</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.80942286365754</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.82476002183327</v>
+        <v>21.0291583811881</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.86488564039168</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.59216792542458</v>
       </c>
     </row>
   </sheetData>
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.12965443959055</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16.68987863851615</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.18049672029077</v>
+        <v>19.13391182980564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.74462586707619</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.65399855104691</v>
       </c>
     </row>
   </sheetData>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.43309257549689</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.85728492283579</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.94411464425751</v>
+        <v>28.78305472952906</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.01684751464565</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.34440461073594</v>
       </c>
     </row>
   </sheetData>
@@ -3992,13 +3992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.88780055260479</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.61431295232833</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.62917276761532</v>
+        <v>22.2121574722048</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.10603694028834</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.77401860556446</v>
       </c>
     </row>
   </sheetData>
@@ -4042,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.19345823408132</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.01998184054873</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.53147106132513</v>
+        <v>23.84617095223238</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.14908324850939</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.58189241430132</v>
       </c>
     </row>
   </sheetData>
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.89661343526062</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15.82587469951517</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.33598720322962</v>
+        <v>21.19378885022169</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.37606456190552</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.93636293010844</v>
       </c>
     </row>
   </sheetData>
@@ -4142,13 +4142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.39917315918827</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.40593679079122</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.96034224713489</v>
+        <v>20.62344640503969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.32527841905859</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.2853386394574</v>
       </c>
     </row>
   </sheetData>
@@ -4192,13 +4192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.11006877200602</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.16085722352696</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.58758017280402</v>
+        <v>19.50074771098795</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.8113934400747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.90768748350517</v>
       </c>
     </row>
   </sheetData>
@@ -4242,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.48667929589364</v>
-      </c>
-      <c r="C2" t="n">
-        <v>17.62135186967467</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.55624081572758</v>
+        <v>21.22607793390283</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.34106017978338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.83622038973015</v>
       </c>
     </row>
   </sheetData>
@@ -4292,13 +4292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.71459838547401</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.4647105091812</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.43926113029865</v>
+        <v>18.86305002045646</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.389877231772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.9070506503657</v>
       </c>
     </row>
   </sheetData>
@@ -4342,13 +4342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.10721392847265</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.83685840374489</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.83987801412736</v>
+        <v>34.86796152687092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.25626589341418</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.47918360250294</v>
       </c>
     </row>
   </sheetData>
@@ -4392,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.66463894181173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.57685998188458</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.81680705904997</v>
+        <v>22.20703848189697</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.5729451462278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.56133104683497</v>
       </c>
     </row>
   </sheetData>
@@ -4442,13 +4442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.37036866718558</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.36657809970418</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.97073517205835</v>
+        <v>17.73387780670596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.34038877030428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.01813327827785</v>
       </c>
     </row>
   </sheetData>
@@ -4492,13 +4492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.64217312134599</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.15050009551107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.41628398078555</v>
+        <v>21.81590281988</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.58753637983145</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.28874717654705</v>
       </c>
     </row>
   </sheetData>
@@ -4542,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.46417736837623</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.39660537499277</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.03445878636449</v>
+        <v>24.83183529816539</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.45710062424993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.89905852237957</v>
       </c>
     </row>
   </sheetData>
@@ -4592,13 +4592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.98976700609475</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.20008758923888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.42524613516096</v>
+        <v>20.23567214910256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.95844439563879</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.06341437896418</v>
       </c>
     </row>
   </sheetData>
@@ -4642,13 +4642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.10992471444893</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.05508978484108</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.23248460090994</v>
+        <v>23.56618115215451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.2771303102156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.12124390014665</v>
       </c>
     </row>
   </sheetData>
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.46915462406644</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.95379913898936</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.13375779926783</v>
+        <v>23.01278027392456</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.00756457096924</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.25696661454154</v>
       </c>
     </row>
   </sheetData>
@@ -4742,13 +4742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.52942255752297</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.30690801522296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.80614039903159</v>
+        <v>20.25839980371173</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.2363434438527</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.15315742150955</v>
       </c>
     </row>
   </sheetData>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.23089785848449</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.25953254286247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.3139648425288</v>
+        <v>24.94093638258108</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.45314855722108</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.7381385064334</v>
       </c>
     </row>
   </sheetData>
@@ -4842,13 +4842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.65296630676276</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16.82078466099746</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.98632317929748</v>
+        <v>22.5905096285156</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.86080460000787</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.00319083709946</v>
       </c>
     </row>
   </sheetData>
@@ -4892,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.82653769831421</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.87206693484615</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.02011183374253</v>
+        <v>17.32058491467969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.87963068475011</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.09065857713011</v>
       </c>
     </row>
   </sheetData>
@@ -4942,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.29222156632604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.30070275939532</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.20540390496978</v>
+        <v>23.35092185706977</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.21284468470687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.3634694191514</v>
       </c>
     </row>
   </sheetData>
@@ -4992,13 +4992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.08662873429117</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.40943466620548</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.03473823191349</v>
+        <v>23.99710361037958</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.81110215557747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.22410387188409</v>
       </c>
     </row>
   </sheetData>
@@ -5042,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.08293322265116</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.34921088436774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.82349168349402</v>
+        <v>22.61796263271181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.07889637439759</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.13971384184872</v>
       </c>
     </row>
   </sheetData>
@@ -5092,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.94534080430794</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.01910530982525</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.40213381312288</v>
+        <v>20.94998130234309</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.23575712932427</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.98515992723572</v>
       </c>
     </row>
   </sheetData>
@@ -5142,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.53226140620225</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.47564391849057</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.95407811925394</v>
+        <v>25.77580140283892</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.83582762263878</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.15250557807313</v>
       </c>
     </row>
   </sheetData>
@@ -5192,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.34503044839576</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.48783387451727</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.00435668521073</v>
+        <v>23.03579183067041</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.83651639682896</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.68268814298672</v>
       </c>
     </row>
   </sheetData>
@@ -5242,13 +5242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.22371001144482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.30825980163042</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.02553249598864</v>
+        <v>20.56264194639208</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.19306331213506</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.21827046559292</v>
       </c>
     </row>
   </sheetData>
@@ -5292,13 +5292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.04495445710794</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.58057258557525</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.05856026591663</v>
+        <v>20.37928439720311</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.40107191742968</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.99704711724646</v>
       </c>
     </row>
   </sheetData>
@@ -5342,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.66663558099425</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.54891749466491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.06732360608257</v>
+        <v>23.17503202018846</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.13631969527509</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.08709936724161</v>
       </c>
     </row>
   </sheetData>
@@ -5392,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.24888203116561</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.19810499304619</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.38344574496609</v>
+        <v>27.74082768864899</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.7547454087741</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.33918135151431</v>
       </c>
     </row>
   </sheetData>
@@ -5442,13 +5442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.46570689182171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.65117900570561</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.04917088201739</v>
+        <v>25.38684536866534</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.88528523001009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.57654067769258</v>
       </c>
     </row>
   </sheetData>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.92601510738172</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.44351918225734</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.59148135795107</v>
+        <v>18.55049268081718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.80565119380704</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.60666068958451</v>
       </c>
     </row>
   </sheetData>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.01984041894128</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.38564489160334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.63962374991276</v>
+        <v>16.10704467316424</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.78588847711793</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.53615209325455</v>
       </c>
     </row>
   </sheetData>
@@ -5592,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.09725991842349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.93174728731705</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.26424897254456</v>
+        <v>25.75655627498314</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.07295194943025</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.96196841716598</v>
       </c>
     </row>
   </sheetData>
@@ -5642,13 +5642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.84295014760078</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.03555686430801</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.63422654388857</v>
+        <v>27.65454349197824</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.40994515248718</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.6318910481627</v>
       </c>
     </row>
   </sheetData>
@@ -5692,13 +5692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.64945107435115</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.27915193956834</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.32396498749132</v>
+        <v>23.63390339867099</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.55382480492205</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.14675982131547</v>
       </c>
     </row>
   </sheetData>
@@ -5742,13 +5742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.0406073121578</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.94975666181343</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.02191474453594</v>
+        <v>20.36300469472378</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.63452928996863</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.5186786447612</v>
       </c>
     </row>
   </sheetData>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.40605762319537</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.92996309106335</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.60168846847741</v>
+        <v>23.9572219728464</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.7343886959306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.34193531950436</v>
       </c>
     </row>
   </sheetData>
@@ -5842,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.38843646099876</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.78363088913962</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.02019371952326</v>
+        <v>22.71584752526539</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.7926153741901</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.18147051232898</v>
       </c>
     </row>
   </sheetData>
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.55565588957053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.14077562863837</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.74612780356495</v>
+        <v>19.95850149344679</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.42860223219153</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.4090879896579</v>
       </c>
     </row>
   </sheetData>
@@ -5942,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.17620922403452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.28789258549509</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.32427967948009</v>
+        <v>29.72509396717476</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.77013409145357</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.68661082573099</v>
       </c>
     </row>
   </sheetData>
@@ -5992,13 +5992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.66886471237598</v>
-      </c>
-      <c r="C2" t="n">
-        <v>17.06340196907843</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.12555933899128</v>
+        <v>18.02091541687626</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.11116105538622</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.05800133441011</v>
       </c>
     </row>
   </sheetData>
@@ -6042,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.91115381182585</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.16737389765959</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.39560617858803</v>
+        <v>22.20983737517315</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.65468268294198</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.23333852282477</v>
       </c>
     </row>
   </sheetData>
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.06612497760953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.78407569922085</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.29327798531081</v>
+        <v>23.40658643479506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.08911688503255</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.7721156427548</v>
       </c>
     </row>
   </sheetData>
@@ -6142,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.48746463560197</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.74898489203786</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.30565869139773</v>
+        <v>19.0567868358018</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.54690546937237</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.94736961342973</v>
       </c>
     </row>
   </sheetData>
@@ -6192,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.24155392424957</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.40974046472162</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.82797950661754</v>
+        <v>24.79575761516885</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.95532388556797</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.5070378448868</v>
       </c>
     </row>
   </sheetData>
@@ -6242,13 +6242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.58177237052604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.99908600977782</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.72665728864947</v>
+        <v>19.22293504715211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.50882958460146</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.21003273488564</v>
       </c>
     </row>
   </sheetData>
@@ -6292,13 +6292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.27802515671529</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.77966195651588</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.17631635820415</v>
+        <v>20.63892754983901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.14880613688867</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.8298222982052</v>
       </c>
     </row>
   </sheetData>
@@ -6342,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.62772510257654</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.92805852174351</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.65677825840124</v>
+        <v>19.62343496909598</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.14542949380088</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.2741676475846</v>
       </c>
     </row>
   </sheetData>
@@ -6392,13 +6392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.38189006707753</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.69369126550865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.91068149946699</v>
+        <v>20.59280628259724</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.4102166286444</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.73619111489217</v>
       </c>
     </row>
   </sheetData>
@@ -6442,13 +6442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.60678069661711</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.54332217333995</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.93568833758394</v>
+        <v>25.76571172923181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.62377219439282</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.98749803563798</v>
       </c>
     </row>
   </sheetData>
@@ -6492,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.41718430835575</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.56309181115533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.08190724062183</v>
+        <v>27.00231313109435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.15581898341194</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.03239409468427</v>
       </c>
     </row>
   </sheetData>
@@ -6542,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.83125307314965</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.16743748877002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.11206678451535</v>
+        <v>26.55713749138069</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.26444350406449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.68628430057309</v>
       </c>
     </row>
   </sheetData>
@@ -6592,13 +6592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.18907795791355</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.77131087987802</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.8793532604307</v>
+        <v>19.87995186440714</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.19202528733592</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.51881615769969</v>
       </c>
     </row>
   </sheetData>
@@ -6642,13 +6642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.09380813554425</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.79570934592626</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.01955653999554</v>
+        <v>20.56810797227596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.65740442886784</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.18124894574606</v>
       </c>
     </row>
   </sheetData>
@@ -6692,13 +6692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.41224520689848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.25116742027149</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.88312141531705</v>
+        <v>25.83250822760334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.09957782678512</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.45477220404261</v>
       </c>
     </row>
   </sheetData>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.68784387467281</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.75390799768533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.98078268758019</v>
+        <v>22.70329853361846</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.4893983873449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.95786305008847</v>
       </c>
     </row>
   </sheetData>
@@ -6792,13 +6792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.18431213850956</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.51740573049687</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.96653534826413</v>
+        <v>19.11570384633027</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.72653245488466</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.91127042067783</v>
       </c>
     </row>
   </sheetData>
@@ -6842,13 +6842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.55713479095029</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.06127557399018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.32151155392437</v>
+        <v>24.24729134342927</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.5332504543073</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.65513790142735</v>
       </c>
     </row>
   </sheetData>
@@ -6892,13 +6892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.34200399542806</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.24337888961653</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.49706292892946</v>
+        <v>20.34005025958981</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.75457370222402</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.98089804887476</v>
       </c>
     </row>
   </sheetData>
@@ -6942,13 +6942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.43295370025422</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.41979438786607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.00315721555533</v>
+        <v>23.89448486362354</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.74795498143215</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.75097669276287</v>
       </c>
     </row>
   </sheetData>
@@ -6992,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.62977953255601</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.58455522662432</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.58903050328047</v>
+        <v>29.78003520387707</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.38116581069173</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.12402027351215</v>
       </c>
     </row>
   </sheetData>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.00028347019328</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.77899459391184</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.54155314419611</v>
+        <v>21.89839112995375</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.99711043934022</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.08301563731496</v>
       </c>
     </row>
   </sheetData>
@@ -7092,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.17802364351613</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.38711327355556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.19849653103963</v>
+        <v>18.72285511651527</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.35346408406875</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.76105930938301</v>
       </c>
     </row>
   </sheetData>
@@ -7142,13 +7142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.79020874858181</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.8763360123302</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.64035060647061</v>
+        <v>27.79077990584302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.75339071977798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.88136462877876</v>
       </c>
     </row>
   </sheetData>
@@ -7192,13 +7192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.08914176863005</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.37536957006883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.82014602978568</v>
+        <v>21.9120502981782</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.20680006472181</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.76842906184633</v>
       </c>
     </row>
   </sheetData>
@@ -7242,13 +7242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.50819186112292</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.1147385442997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.82861033866125</v>
+        <v>19.44175294888361</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.31986188292599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.68787996953534</v>
       </c>
     </row>
   </sheetData>
@@ -7292,13 +7292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.31859281339443</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.97847481156325</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.18137927754114</v>
+        <v>23.96184797777165</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.87450315692069</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.76230279894002</v>
       </c>
     </row>
   </sheetData>
@@ -7342,13 +7342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.77941406791779</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.52206043808184</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.95964305554565</v>
+        <v>19.94666315233257</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.31926581905606</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.15147987451761</v>
       </c>
     </row>
   </sheetData>
@@ -7392,13 +7392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.03613492298344</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.09340601966469</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.28311098889188</v>
+        <v>24.99010449704049</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.88297630502865</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.01427917512165</v>
       </c>
     </row>
   </sheetData>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.66631609568426</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.65139887119922</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.29792174903632</v>
+        <v>30.37462218087012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.28073607903753</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.42536327024472</v>
       </c>
     </row>
   </sheetData>
@@ -7492,13 +7492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.18832532498334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.90275421371634</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.95390249283485</v>
+        <v>25.44535745595522</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.4720350635183</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.76080246185071</v>
       </c>
     </row>
   </sheetData>
@@ -7542,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.70660802613432</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.00601856624995</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.81095810709999</v>
+        <v>21.31467894976188</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.1859606815307</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.77516246403232</v>
       </c>
     </row>
   </sheetData>
@@ -7592,13 +7592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.75702876948419</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.87278501153757</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.64176263604087</v>
+        <v>21.33621498906155</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.0693071132916</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.3561421015806</v>
       </c>
     </row>
   </sheetData>
@@ -7642,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.84152113986404</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.34289646445907</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.95630343627347</v>
+        <v>21.74520101977825</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.14523551996249</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.61976992011225</v>
       </c>
     </row>
   </sheetData>
@@ -7692,13 +7692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.95190386296263</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.03646648117412</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.16618887121192</v>
+        <v>21.18372436578463</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.88998818760986</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.75069518221195</v>
       </c>
     </row>
   </sheetData>
@@ -7742,13 +7742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.29402241911286</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.37772070289979</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.40437097393082</v>
+        <v>18.05754631267668</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.9774286878463</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.41008115697912</v>
       </c>
     </row>
   </sheetData>
@@ -7792,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.91677459011696</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.07253230133967</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.27665842713071</v>
+        <v>20.88556613747199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.28456413129654</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.53852221544837</v>
       </c>
     </row>
   </sheetData>
@@ -7842,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.68018129430926</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.15350299599178</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.35961616743013</v>
+        <v>21.63503500698992</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.63483100729074</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.66018174715394</v>
       </c>
     </row>
   </sheetData>
@@ -7892,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.30745360618821</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.37457067521473</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.67752134413266</v>
+        <v>20.03877852955052</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.65115996104501</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.67817576069298</v>
       </c>
     </row>
   </sheetData>
@@ -7942,13 +7942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.51509759740698</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.76286640388281</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.53970882707786</v>
+        <v>17.08329784729039</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.73249152993497</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.20045622976233</v>
       </c>
     </row>
   </sheetData>
@@ -7992,13 +7992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.28853968204374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.93363333678308</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.23540915360813</v>
+        <v>28.42085282647388</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.0715081682245</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.28147260547521</v>
       </c>
     </row>
   </sheetData>
@@ -8042,13 +8042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.16912604203361</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.3159966302766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.1668152256101</v>
+        <v>20.18182830980099</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.50532873129873</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.21631125166116</v>
       </c>
     </row>
   </sheetData>
@@ -8092,13 +8092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.89008305338607</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.49912625448871</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.18652893867061</v>
+        <v>25.21954814865343</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.67258247743871</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.3787240340063</v>
       </c>
     </row>
   </sheetData>
@@ -8142,13 +8142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.37846082251379</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.71377037648277</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.87420352611479</v>
+        <v>18.48033862620944</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.8419412890844</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.07622774982643</v>
       </c>
     </row>
   </sheetData>
@@ -8192,13 +8192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.25185761575083</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.35049349526711</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.6219900656521</v>
+        <v>19.77696356258333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.44092553836023</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.65646009921698</v>
       </c>
     </row>
   </sheetData>
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.21821691838957</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.71718358992914</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.89571416088433</v>
+        <v>19.5853960258773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.45240441553269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.57398302893958</v>
       </c>
     </row>
   </sheetData>
@@ -8292,13 +8292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.29837340125731</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.49059768713598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.35944855206496</v>
+        <v>21.19741616541534</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.8496875408641</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.75350226266974</v>
       </c>
     </row>
   </sheetData>
@@ -8342,13 +8342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.21792560191299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.35094727281337</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.21331301752042</v>
+        <v>29.82806583782114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.706985141456</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.93532210005397</v>
       </c>
     </row>
   </sheetData>
@@ -8392,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.86151915098231</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.9970074638257</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.73293450260856</v>
+        <v>14.89138236370202</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.53110986969676</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.99029828519781</v>
       </c>
     </row>
   </sheetData>
@@ -8442,13 +8442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.14618056291231</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.81693738383894</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.42327277957905</v>
+        <v>19.82267397084231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.95050432718226</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.65215576786471</v>
       </c>
     </row>
   </sheetData>
@@ -8492,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.03638439588645</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.04406901363239</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.02493243212789</v>
+        <v>27.78590725625953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.73903138030521</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.28705936726029</v>
       </c>
     </row>
   </sheetData>
@@ -8542,13 +8542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.12426751951305</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.52509684147509</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.95701549287211</v>
+        <v>16.6867258673639</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.6285469281454</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.8456488090459</v>
       </c>
     </row>
   </sheetData>
@@ -8592,13 +8592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.77280973337545</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.18014623289976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.00770230296507</v>
+        <v>28.19810898637325</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.51709284741425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.51888043654487</v>
       </c>
     </row>
   </sheetData>
@@ -8642,13 +8642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.25813170776703</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.52205297098083</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.45073546548296</v>
+        <v>23.64047096497753</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.90221528591419</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.57621760309757</v>
       </c>
     </row>
   </sheetData>
@@ -8692,13 +8692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.66233939315821</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.22774070395864</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.11056433939066</v>
+        <v>22.66348672204866</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.99273557404579</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.62399509225227</v>
       </c>
     </row>
   </sheetData>
@@ -8742,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.50661027011892</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.20780342110491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.9157365519017</v>
+        <v>22.07463094821438</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.98900481718714</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.08000365335933</v>
       </c>
     </row>
   </sheetData>
@@ -8792,13 +8792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.1762330268907</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.14453951271887</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.62746829815487</v>
+        <v>23.79762327731885</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.88055451122178</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.22149102388374</v>
       </c>
     </row>
   </sheetData>
@@ -8842,13 +8842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.69096377632725</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.66494523807498</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.86329606015087</v>
+        <v>17.538424703042</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.29700373618786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.28243400286106</v>
       </c>
     </row>
   </sheetData>
@@ -8892,13 +8892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.11550043174823</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.64422600398576</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.53135297231751</v>
+        <v>22.11107905521287</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.80829163873104</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.37568697544616</v>
       </c>
     </row>
   </sheetData>
@@ -8942,13 +8942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.66970596744362</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.97456535866329</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.03163031641209</v>
+        <v>23.16061545075478</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.77415587142569</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.28143191866746</v>
       </c>
     </row>
   </sheetData>
@@ -8992,13 +8992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.58427262952565</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.55329819149009</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.26497684966367</v>
+        <v>23.04466586589898</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.54140291627496</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.53182504676689</v>
       </c>
     </row>
   </sheetData>
@@ -9042,13 +9042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.06250099608088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.92554791704165</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.9926738737196</v>
+        <v>22.37697123208543</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.38713136283944</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.56026802886137</v>
       </c>
     </row>
   </sheetData>
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.83760979962302</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.62709687454529</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.28327243707647</v>
+        <v>21.29432336852135</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.71315647246158</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.28965480847966</v>
       </c>
     </row>
   </sheetData>
@@ -9142,13 +9142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.10402479677138</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.59130145641136</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.8080285758173</v>
+        <v>25.71794047285356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.72620290169245</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.5958891849228</v>
       </c>
     </row>
   </sheetData>
@@ -9192,13 +9192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.42463739084916</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.93541736605686</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.56151607671166</v>
+        <v>18.84648976848758</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.14968882842515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.91928228050764</v>
       </c>
     </row>
   </sheetData>
@@ -9242,13 +9242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.79764675002102</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.95641604890854</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.79091350696433</v>
+        <v>26.2521655695227</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.49465117963864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.84941094930954</v>
       </c>
     </row>
   </sheetData>
@@ -9292,13 +9292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.1249071308066</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.73819955878229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.41376309662715</v>
+        <v>21.78687195323236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.6193745074872</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.02731452409146</v>
       </c>
     </row>
   </sheetData>
@@ -9342,13 +9342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.43892505626168</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.99669221316107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.917619185075</v>
+        <v>20.08733788948767</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.84551900028184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.11910056807262</v>
       </c>
     </row>
   </sheetData>
@@ -9392,13 +9392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.2806696055982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.92808438009735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.43412090033671</v>
+        <v>26.84735217254053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.61342991612037</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.23315232290549</v>
       </c>
     </row>
   </sheetData>
@@ -9442,13 +9442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.81640902718211</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.07964143137731</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.39615432765479</v>
+        <v>26.7290170740859</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.72101267545037</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.38361538021664</v>
       </c>
     </row>
   </sheetData>
@@ -9492,13 +9492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.11819776680957</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.03256780024597</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.42829991285216</v>
+        <v>18.12702788940353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.54008611986074</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.6068954530363</v>
       </c>
     </row>
   </sheetData>
@@ -9542,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.52453813473173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.09817817358969</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.15320831555184</v>
+        <v>25.97084061679001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.71253533154676</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.03617253979491</v>
       </c>
     </row>
   </sheetData>
@@ -9592,13 +9592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.33765225921457</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.43306539009231</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.82376765587544</v>
+        <v>28.34648309698147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.65151902447238</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.12546899366277</v>
       </c>
     </row>
   </sheetData>
@@ -9642,13 +9642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.37806611636798</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.77820724034018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.04964443811878</v>
+        <v>27.34486495286399</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.35969790283003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.46398124124504</v>
       </c>
     </row>
   </sheetData>
@@ -9692,13 +9692,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.84890446384956</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.85092134745066</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.15515722788284</v>
+        <v>22.83975753028188</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.25498691592523</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.97285421721046</v>
       </c>
     </row>
   </sheetData>
@@ -9742,13 +9742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.82800750387396</v>
-      </c>
-      <c r="C2" t="n">
-        <v>14.62332098003935</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.64465044642884</v>
+        <v>20.58465009292101</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.6328603765918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.00963681597158</v>
       </c>
     </row>
   </sheetData>
@@ -9792,13 +9792,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.49621260240595</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.42400718646268</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.12703835232413</v>
+        <v>23.98759960016723</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.24768052131905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.39352115195815</v>
       </c>
     </row>
   </sheetData>
@@ -9842,13 +9842,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.80455647861453</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.21338820770614</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.83827318697061</v>
+        <v>26.20197042616092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.23428468499328</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.63598278671747</v>
       </c>
     </row>
   </sheetData>
@@ -9892,13 +9892,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.07385424992928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.10887600299875</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.61696758660021</v>
+        <v>26.27201012751401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.43652452750934</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.81165256009826</v>
       </c>
     </row>
   </sheetData>
@@ -9942,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.62993308642147</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.45801806132866</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.08342917639991</v>
+        <v>27.82066493926655</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.39922247682232</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.96289504030613</v>
       </c>
     </row>
   </sheetData>
@@ -9992,13 +9992,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.2720850891397</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.35699832048771</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.44722938413592</v>
+        <v>20.21852060070938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.60766482972788</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.49734773342902</v>
       </c>
     </row>
   </sheetData>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.92429675082286</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.87960552515594</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.04593619715587</v>
+        <v>24.78762077525591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.62000094243704</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.7284972954679</v>
       </c>
     </row>
   </sheetData>
@@ -10092,13 +10092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.73342097094839</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.08841397550784</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.41844528522946</v>
+        <v>27.54411227459675</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.50353067995027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.0153879874682</v>
       </c>
     </row>
   </sheetData>
@@ -10142,13 +10142,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.84758656484168</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.07550475109457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.89490821521093</v>
+        <v>22.08174210246872</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.74234653108165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.04528804103016</v>
       </c>
     </row>
   </sheetData>
@@ -10192,13 +10192,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.79480311036295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.50578046485725</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.99128259366315</v>
+        <v>20.20668360623221</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.37819904433649</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.44325352621723</v>
       </c>
     </row>
   </sheetData>
@@ -10242,13 +10242,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.31804506045219</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.05785198720015</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.28669305715586</v>
+        <v>20.28964221302525</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.87038417907146</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.72328727125822</v>
       </c>
     </row>
   </sheetData>
@@ -10292,13 +10292,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.5524929718785</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.55037960398354</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.3299765695464</v>
+        <v>25.15918029270644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.32861933153792</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.29804851166714</v>
       </c>
     </row>
   </sheetData>
@@ -10342,13 +10342,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.07761843202305</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.25643493319888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.92810899418152</v>
+        <v>21.28717170208409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.9912862784152</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.94991391491155</v>
       </c>
     </row>
   </sheetData>
@@ -10392,13 +10392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.9209002158592</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.59498679868985</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.86973123670533</v>
+        <v>25.06714305646604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.81641111800294</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.85841463737171</v>
       </c>
     </row>
   </sheetData>
@@ -10442,13 +10442,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.67157627765875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.60344025671011</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.18267858437782</v>
+        <v>20.84699041360835</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.28650845520313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.54990691218736</v>
       </c>
     </row>
   </sheetData>
@@ -10492,13 +10492,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.2016680142622</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.87517254994919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.70925150658866</v>
+        <v>19.3461361185242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.30177077514224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.56980538535515</v>
       </c>
     </row>
   </sheetData>
@@ -10542,13 +10542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.09968604794853</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.76703432479522</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.58675441082478</v>
+        <v>23.08902739094227</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.58561804605174</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.98931101646416</v>
       </c>
     </row>
   </sheetData>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.2250740395055</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.1355855227999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.65681116674646</v>
+        <v>21.11747382075638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.50938134084864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.60305376164397</v>
       </c>
     </row>
   </sheetData>
